--- a/public_html/assets/archivo/corte/40-GASOLINAS/40-GASOLINAS_01-2025_01.xlsx
+++ b/public_html/assets/archivo/corte/40-GASOLINAS/40-GASOLINAS_01-2025_01.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="203">
   <si>
     <t>PAGO</t>
   </si>
@@ -106,6 +106,12 @@
     <t>137290104379143332</t>
   </si>
   <si>
+    <t>GERARDO DANIEL   HERMIDA AMADOR</t>
+  </si>
+  <si>
+    <t>012180015298596151</t>
+  </si>
+  <si>
     <t>MA GUADALUPE   VAZQUEZ FLORES</t>
   </si>
   <si>
@@ -238,6 +244,12 @@
     <t>012760026196083706</t>
   </si>
   <si>
+    <t>MARIA FLORA  QUINTANA  ORTEGA</t>
+  </si>
+  <si>
+    <t>012760015037062444</t>
+  </si>
+  <si>
     <t>PATRICIA  ALCOCER  CARVAJAL</t>
   </si>
   <si>
@@ -310,6 +322,12 @@
     <t>137180290075203260</t>
   </si>
   <si>
+    <t>FELIPE     BUENO SALGADO</t>
+  </si>
+  <si>
+    <t>012180015035561501</t>
+  </si>
+  <si>
     <t>OMAR ALEJANDRO GARCIA  SANDOVAL</t>
   </si>
   <si>
@@ -331,6 +349,12 @@
     <t>012180015819251927</t>
   </si>
   <si>
+    <t xml:space="preserve">LAURA NAVARRETE BARCENAS  </t>
+  </si>
+  <si>
+    <t>127261013100918918</t>
+  </si>
+  <si>
     <t xml:space="preserve">DENNYS PAOLA GARCIA ALCAZAR  </t>
   </si>
   <si>
@@ -385,6 +409,12 @@
     <t>127180013615689318</t>
   </si>
   <si>
+    <t>ANGEL  BUSTOS ESTRADA</t>
+  </si>
+  <si>
+    <t>072261002882844880</t>
+  </si>
+  <si>
     <t xml:space="preserve">HECTOR MANUEL FERNANDEZ ARMENTA  </t>
   </si>
   <si>
@@ -410,6 +440,9 @@
   </si>
   <si>
     <t>137020103623464077</t>
+  </si>
+  <si>
+    <t>ELIOTT EMMANUEL RENDON AVILA</t>
   </si>
   <si>
     <t>MIGUEL  VAZQUEZ  VILLA</t>
@@ -977,7 +1010,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="1"/>
@@ -1030,7 +1063,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1">
-        <v>91759</v>
+        <v>92606</v>
       </c>
       <c r="B2" s="1">
         <v>3146</v>
@@ -1065,7 +1098,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1">
-        <v>91770</v>
+        <v>92616</v>
       </c>
       <c r="B3" s="1">
         <v>4209</v>
@@ -1100,7 +1133,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1">
-        <v>91791</v>
+        <v>92635</v>
       </c>
       <c r="B4" s="1">
         <v>8272</v>
@@ -1135,7 +1168,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1">
-        <v>91805</v>
+        <v>92644</v>
       </c>
       <c r="B5" s="1">
         <v>11101</v>
@@ -1170,7 +1203,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1">
-        <v>91794</v>
+        <v>92638</v>
       </c>
       <c r="B6" s="1">
         <v>12634</v>
@@ -1205,7 +1238,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1">
-        <v>91811</v>
+        <v>92650</v>
       </c>
       <c r="B7" s="1">
         <v>14975</v>
@@ -1240,10 +1273,10 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1">
-        <v>91799</v>
+        <v>92595</v>
       </c>
       <c r="B8" s="1">
-        <v>25919</v>
+        <v>17042</v>
       </c>
       <c r="C8" t="s">
         <v>29</v>
@@ -1258,16 +1291,16 @@
         <v>13</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H8" s="3">
-        <v>690.0</v>
+        <v>150.0</v>
       </c>
       <c r="I8" s="3">
-        <v>36.46</v>
+        <v>2.88</v>
       </c>
       <c r="J8" s="3">
-        <v>653.54</v>
+        <v>147.12</v>
       </c>
       <c r="K8" t="s">
         <v>15</v>
@@ -1275,34 +1308,34 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1">
-        <v>91765</v>
+        <v>92641</v>
       </c>
       <c r="B9" s="1">
-        <v>26120</v>
+        <v>25919</v>
       </c>
       <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="1">
+        <v>30</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="1">
-        <v>30</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="H9" s="3">
-        <v>400.0</v>
+        <v>690.0</v>
       </c>
       <c r="I9" s="3">
-        <v>17.9</v>
+        <v>36.46</v>
       </c>
       <c r="J9" s="3">
-        <v>382.1</v>
+        <v>653.54</v>
       </c>
       <c r="K9" t="s">
         <v>15</v>
@@ -1310,10 +1343,10 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1">
-        <v>91815</v>
+        <v>92612</v>
       </c>
       <c r="B10" s="1">
-        <v>27736</v>
+        <v>26120</v>
       </c>
       <c r="C10" t="s">
         <v>34</v>
@@ -1328,16 +1361,16 @@
         <v>13</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H10" s="3">
-        <v>140.0</v>
+        <v>400.0</v>
       </c>
       <c r="I10" s="3">
-        <v>2.69</v>
+        <v>17.9</v>
       </c>
       <c r="J10" s="3">
-        <v>137.31</v>
+        <v>382.1</v>
       </c>
       <c r="K10" t="s">
         <v>15</v>
@@ -1345,10 +1378,10 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1">
-        <v>91801</v>
+        <v>92588</v>
       </c>
       <c r="B11" s="1">
-        <v>28458</v>
+        <v>27736</v>
       </c>
       <c r="C11" t="s">
         <v>36</v>
@@ -1363,7 +1396,7 @@
         <v>13</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H11" s="3">
         <v>240.0</v>
@@ -1380,34 +1413,34 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1">
-        <v>91802</v>
+        <v>92643</v>
       </c>
       <c r="B12" s="1">
-        <v>28629</v>
+        <v>28458</v>
       </c>
       <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="1">
+        <v>30</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="1">
-        <v>30</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="H12" s="3">
-        <v>200.0</v>
+        <v>240.0</v>
       </c>
       <c r="I12" s="3">
-        <v>5.1</v>
+        <v>7.66</v>
       </c>
       <c r="J12" s="3">
-        <v>194.9</v>
+        <v>232.34</v>
       </c>
       <c r="K12" t="s">
         <v>15</v>
@@ -1415,10 +1448,10 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1">
-        <v>91769</v>
+        <v>92600</v>
       </c>
       <c r="B13" s="1">
-        <v>30443</v>
+        <v>28629</v>
       </c>
       <c r="C13" t="s">
         <v>41</v>
@@ -1436,13 +1469,13 @@
         <v>18</v>
       </c>
       <c r="H13" s="3">
-        <v>550.0</v>
+        <v>250.0</v>
       </c>
       <c r="I13" s="3">
-        <v>27.5</v>
+        <v>8.3</v>
       </c>
       <c r="J13" s="3">
-        <v>522.5</v>
+        <v>241.7</v>
       </c>
       <c r="K13" t="s">
         <v>15</v>
@@ -1450,10 +1483,10 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1">
-        <v>91764</v>
+        <v>92615</v>
       </c>
       <c r="B14" s="1">
-        <v>31177</v>
+        <v>30443</v>
       </c>
       <c r="C14" t="s">
         <v>43</v>
@@ -1468,16 +1501,16 @@
         <v>13</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H14" s="3">
-        <v>390.0</v>
+        <v>550.0</v>
       </c>
       <c r="I14" s="3">
-        <v>17.26</v>
+        <v>27.5</v>
       </c>
       <c r="J14" s="3">
-        <v>372.74</v>
+        <v>522.5</v>
       </c>
       <c r="K14" t="s">
         <v>15</v>
@@ -1485,10 +1518,10 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1">
-        <v>91810</v>
+        <v>92611</v>
       </c>
       <c r="B15" s="1">
-        <v>31645</v>
+        <v>31177</v>
       </c>
       <c r="C15" t="s">
         <v>45</v>
@@ -1506,13 +1539,13 @@
         <v>21</v>
       </c>
       <c r="H15" s="3">
-        <v>240.0</v>
+        <v>390.0</v>
       </c>
       <c r="I15" s="3">
-        <v>7.66</v>
+        <v>17.26</v>
       </c>
       <c r="J15" s="3">
-        <v>232.34</v>
+        <v>372.74</v>
       </c>
       <c r="K15" t="s">
         <v>15</v>
@@ -1520,10 +1553,10 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1">
-        <v>91786</v>
+        <v>92649</v>
       </c>
       <c r="B16" s="1">
-        <v>31758</v>
+        <v>31645</v>
       </c>
       <c r="C16" t="s">
         <v>47</v>
@@ -1538,16 +1571,16 @@
         <v>13</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H16" s="3">
-        <v>480.0</v>
+        <v>240.0</v>
       </c>
       <c r="I16" s="3">
-        <v>23.02</v>
+        <v>7.66</v>
       </c>
       <c r="J16" s="3">
-        <v>456.98</v>
+        <v>232.34</v>
       </c>
       <c r="K16" t="s">
         <v>15</v>
@@ -1555,10 +1588,10 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1">
-        <v>91803</v>
+        <v>92631</v>
       </c>
       <c r="B17" s="1">
-        <v>31868</v>
+        <v>31758</v>
       </c>
       <c r="C17" t="s">
         <v>49</v>
@@ -1573,16 +1606,16 @@
         <v>13</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H17" s="3">
-        <v>820.0</v>
+        <v>480.0</v>
       </c>
       <c r="I17" s="3">
-        <v>44.78</v>
+        <v>23.02</v>
       </c>
       <c r="J17" s="3">
-        <v>775.22</v>
+        <v>456.98</v>
       </c>
       <c r="K17" t="s">
         <v>15</v>
@@ -1590,10 +1623,10 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1">
-        <v>91828</v>
+        <v>92599</v>
       </c>
       <c r="B18" s="1">
-        <v>31888</v>
+        <v>31868</v>
       </c>
       <c r="C18" t="s">
         <v>51</v>
@@ -1608,16 +1641,16 @@
         <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H18" s="3">
-        <v>120.0</v>
+        <v>870.0</v>
       </c>
       <c r="I18" s="3">
-        <v>2.3</v>
+        <v>47.98</v>
       </c>
       <c r="J18" s="3">
-        <v>117.7</v>
+        <v>822.02</v>
       </c>
       <c r="K18" t="s">
         <v>15</v>
@@ -1625,10 +1658,10 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="1">
-        <v>91819</v>
+        <v>92662</v>
       </c>
       <c r="B19" s="1">
-        <v>32042</v>
+        <v>31888</v>
       </c>
       <c r="C19" t="s">
         <v>53</v>
@@ -1643,16 +1676,16 @@
         <v>13</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H19" s="3">
-        <v>330.0</v>
+        <v>120.0</v>
       </c>
       <c r="I19" s="3">
-        <v>13.42</v>
+        <v>2.3</v>
       </c>
       <c r="J19" s="3">
-        <v>316.58</v>
+        <v>117.7</v>
       </c>
       <c r="K19" t="s">
         <v>15</v>
@@ -1660,10 +1693,10 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1">
-        <v>91838</v>
+        <v>92656</v>
       </c>
       <c r="B20" s="1">
-        <v>32228</v>
+        <v>32042</v>
       </c>
       <c r="C20" t="s">
         <v>55</v>
@@ -1678,16 +1711,16 @@
         <v>13</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H20" s="3">
-        <v>800.0</v>
+        <v>330.0</v>
       </c>
       <c r="I20" s="3">
-        <v>43.5</v>
+        <v>13.42</v>
       </c>
       <c r="J20" s="3">
-        <v>756.5</v>
+        <v>316.58</v>
       </c>
       <c r="K20" t="s">
         <v>15</v>
@@ -1695,10 +1728,10 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="1">
-        <v>91831</v>
+        <v>92672</v>
       </c>
       <c r="B21" s="1">
-        <v>32565</v>
+        <v>32228</v>
       </c>
       <c r="C21" t="s">
         <v>57</v>
@@ -1713,16 +1746,16 @@
         <v>13</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H21" s="3">
-        <v>380.0</v>
+        <v>800.0</v>
       </c>
       <c r="I21" s="3">
-        <v>16.62</v>
+        <v>43.5</v>
       </c>
       <c r="J21" s="3">
-        <v>363.38</v>
+        <v>756.5</v>
       </c>
       <c r="K21" t="s">
         <v>15</v>
@@ -1730,10 +1763,10 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="1">
-        <v>91812</v>
+        <v>92665</v>
       </c>
       <c r="B22" s="1">
-        <v>32782</v>
+        <v>32565</v>
       </c>
       <c r="C22" t="s">
         <v>59</v>
@@ -1748,16 +1781,16 @@
         <v>13</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H22" s="3">
-        <v>150.0</v>
+        <v>380.0</v>
       </c>
       <c r="I22" s="3">
-        <v>2.88</v>
+        <v>16.62</v>
       </c>
       <c r="J22" s="3">
-        <v>147.12</v>
+        <v>363.38</v>
       </c>
       <c r="K22" t="s">
         <v>15</v>
@@ -1765,10 +1798,10 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="1">
-        <v>91785</v>
+        <v>92651</v>
       </c>
       <c r="B23" s="1">
-        <v>33949</v>
+        <v>32782</v>
       </c>
       <c r="C23" t="s">
         <v>61</v>
@@ -1783,16 +1816,16 @@
         <v>13</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H23" s="3">
-        <v>250.0</v>
+        <v>150.0</v>
       </c>
       <c r="I23" s="3">
-        <v>8.3</v>
+        <v>2.88</v>
       </c>
       <c r="J23" s="3">
-        <v>241.7</v>
+        <v>147.12</v>
       </c>
       <c r="K23" t="s">
         <v>15</v>
@@ -1800,10 +1833,10 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1">
-        <v>91784</v>
+        <v>92630</v>
       </c>
       <c r="B24" s="1">
-        <v>34105</v>
+        <v>33949</v>
       </c>
       <c r="C24" t="s">
         <v>63</v>
@@ -1818,16 +1851,16 @@
         <v>13</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H24" s="3">
-        <v>300.0</v>
+        <v>250.0</v>
       </c>
       <c r="I24" s="3">
-        <v>11.5</v>
+        <v>8.3</v>
       </c>
       <c r="J24" s="3">
-        <v>288.5</v>
+        <v>241.7</v>
       </c>
       <c r="K24" t="s">
         <v>15</v>
@@ -1835,10 +1868,10 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="1">
-        <v>91768</v>
+        <v>92629</v>
       </c>
       <c r="B25" s="1">
-        <v>35957</v>
+        <v>34105</v>
       </c>
       <c r="C25" t="s">
         <v>65</v>
@@ -1853,16 +1886,16 @@
         <v>13</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H25" s="3">
-        <v>440.0</v>
+        <v>300.0</v>
       </c>
       <c r="I25" s="3">
-        <v>20.46</v>
+        <v>11.5</v>
       </c>
       <c r="J25" s="3">
-        <v>419.54</v>
+        <v>288.5</v>
       </c>
       <c r="K25" t="s">
         <v>15</v>
@@ -1870,10 +1903,10 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1">
-        <v>91767</v>
+        <v>92614</v>
       </c>
       <c r="B26" s="1">
-        <v>37206</v>
+        <v>35957</v>
       </c>
       <c r="C26" t="s">
         <v>67</v>
@@ -1888,16 +1921,16 @@
         <v>13</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H26" s="3">
-        <v>150.0</v>
+        <v>440.0</v>
       </c>
       <c r="I26" s="3">
-        <v>2.88</v>
+        <v>20.46</v>
       </c>
       <c r="J26" s="3">
-        <v>147.12</v>
+        <v>419.54</v>
       </c>
       <c r="K26" t="s">
         <v>15</v>
@@ -1905,10 +1938,10 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1">
-        <v>91795</v>
+        <v>92587</v>
       </c>
       <c r="B27" s="1">
-        <v>39687</v>
+        <v>37206</v>
       </c>
       <c r="C27" t="s">
         <v>69</v>
@@ -1923,16 +1956,16 @@
         <v>13</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H27" s="3">
-        <v>120.0</v>
+        <v>250.0</v>
       </c>
       <c r="I27" s="3">
-        <v>2.3</v>
+        <v>8.3</v>
       </c>
       <c r="J27" s="3">
-        <v>117.7</v>
+        <v>241.7</v>
       </c>
       <c r="K27" t="s">
         <v>15</v>
@@ -1940,10 +1973,10 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="1">
-        <v>91804</v>
+        <v>92596</v>
       </c>
       <c r="B28" s="1">
-        <v>41172</v>
+        <v>39687</v>
       </c>
       <c r="C28" t="s">
         <v>71</v>
@@ -1961,13 +1994,13 @@
         <v>18</v>
       </c>
       <c r="H28" s="3">
-        <v>140.0</v>
+        <v>170.0</v>
       </c>
       <c r="I28" s="3">
-        <v>2.69</v>
+        <v>3.26</v>
       </c>
       <c r="J28" s="3">
-        <v>137.31</v>
+        <v>166.74</v>
       </c>
       <c r="K28" t="s">
         <v>15</v>
@@ -1975,10 +2008,10 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="1">
-        <v>91772</v>
+        <v>92593</v>
       </c>
       <c r="B29" s="1">
-        <v>41929</v>
+        <v>41172</v>
       </c>
       <c r="C29" t="s">
         <v>73</v>
@@ -1996,13 +2029,13 @@
         <v>18</v>
       </c>
       <c r="H29" s="3">
-        <v>740.0</v>
+        <v>230.0</v>
       </c>
       <c r="I29" s="3">
-        <v>39.66</v>
+        <v>7.02</v>
       </c>
       <c r="J29" s="3">
-        <v>700.34</v>
+        <v>222.98</v>
       </c>
       <c r="K29" t="s">
         <v>15</v>
@@ -2010,10 +2043,10 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1">
-        <v>91827</v>
+        <v>92592</v>
       </c>
       <c r="B30" s="1">
-        <v>42170</v>
+        <v>41428</v>
       </c>
       <c r="C30" t="s">
         <v>75</v>
@@ -2031,13 +2064,13 @@
         <v>18</v>
       </c>
       <c r="H30" s="3">
-        <v>320.0</v>
+        <v>120.0</v>
       </c>
       <c r="I30" s="3">
-        <v>12.78</v>
+        <v>2.3</v>
       </c>
       <c r="J30" s="3">
-        <v>307.22</v>
+        <v>117.7</v>
       </c>
       <c r="K30" t="s">
         <v>15</v>
@@ -2045,10 +2078,10 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="1">
-        <v>91830</v>
+        <v>92618</v>
       </c>
       <c r="B31" s="1">
-        <v>42575</v>
+        <v>41929</v>
       </c>
       <c r="C31" t="s">
         <v>77</v>
@@ -2063,16 +2096,16 @@
         <v>13</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H31" s="3">
-        <v>620.0</v>
+        <v>740.0</v>
       </c>
       <c r="I31" s="3">
-        <v>31.98</v>
+        <v>39.66</v>
       </c>
       <c r="J31" s="3">
-        <v>588.02</v>
+        <v>700.34</v>
       </c>
       <c r="K31" t="s">
         <v>15</v>
@@ -2080,10 +2113,10 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="1">
-        <v>91834</v>
+        <v>92604</v>
       </c>
       <c r="B32" s="1">
-        <v>42628</v>
+        <v>42170</v>
       </c>
       <c r="C32" t="s">
         <v>79</v>
@@ -2101,13 +2134,13 @@
         <v>18</v>
       </c>
       <c r="H32" s="3">
-        <v>720.0</v>
+        <v>420.0</v>
       </c>
       <c r="I32" s="3">
-        <v>38.38</v>
+        <v>19.18</v>
       </c>
       <c r="J32" s="3">
-        <v>681.62</v>
+        <v>400.82</v>
       </c>
       <c r="K32" t="s">
         <v>15</v>
@@ -2115,10 +2148,10 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="1">
-        <v>91836</v>
+        <v>92664</v>
       </c>
       <c r="B33" s="1">
-        <v>43119</v>
+        <v>42575</v>
       </c>
       <c r="C33" t="s">
         <v>81</v>
@@ -2136,13 +2169,13 @@
         <v>14</v>
       </c>
       <c r="H33" s="3">
-        <v>150.0</v>
+        <v>620.0</v>
       </c>
       <c r="I33" s="3">
-        <v>2.88</v>
+        <v>31.98</v>
       </c>
       <c r="J33" s="3">
-        <v>147.12</v>
+        <v>588.02</v>
       </c>
       <c r="K33" t="s">
         <v>15</v>
@@ -2150,10 +2183,10 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="1">
-        <v>91813</v>
+        <v>92668</v>
       </c>
       <c r="B34" s="1">
-        <v>44798</v>
+        <v>42628</v>
       </c>
       <c r="C34" t="s">
         <v>83</v>
@@ -2171,13 +2204,13 @@
         <v>18</v>
       </c>
       <c r="H34" s="3">
-        <v>250.0</v>
+        <v>720.0</v>
       </c>
       <c r="I34" s="3">
-        <v>8.3</v>
+        <v>38.38</v>
       </c>
       <c r="J34" s="3">
-        <v>241.7</v>
+        <v>681.62</v>
       </c>
       <c r="K34" t="s">
         <v>15</v>
@@ -2185,10 +2218,10 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="1">
-        <v>91783</v>
+        <v>92670</v>
       </c>
       <c r="B35" s="1">
-        <v>45670</v>
+        <v>43119</v>
       </c>
       <c r="C35" t="s">
         <v>85</v>
@@ -2203,16 +2236,16 @@
         <v>13</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H35" s="3">
-        <v>380.0</v>
+        <v>150.0</v>
       </c>
       <c r="I35" s="3">
-        <v>16.62</v>
+        <v>2.88</v>
       </c>
       <c r="J35" s="3">
-        <v>363.38</v>
+        <v>147.12</v>
       </c>
       <c r="K35" t="s">
         <v>15</v>
@@ -2220,10 +2253,10 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="1">
-        <v>91809</v>
+        <v>92652</v>
       </c>
       <c r="B36" s="1">
-        <v>45926</v>
+        <v>44798</v>
       </c>
       <c r="C36" t="s">
         <v>87</v>
@@ -2238,16 +2271,16 @@
         <v>13</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H36" s="3">
-        <v>150.0</v>
+        <v>250.0</v>
       </c>
       <c r="I36" s="3">
-        <v>2.88</v>
+        <v>8.3</v>
       </c>
       <c r="J36" s="3">
-        <v>147.12</v>
+        <v>241.7</v>
       </c>
       <c r="K36" t="s">
         <v>15</v>
@@ -2255,10 +2288,10 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="1">
-        <v>91763</v>
+        <v>92628</v>
       </c>
       <c r="B37" s="1">
-        <v>46498</v>
+        <v>45670</v>
       </c>
       <c r="C37" t="s">
         <v>89</v>
@@ -2273,16 +2306,16 @@
         <v>13</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H37" s="3">
-        <v>500.0</v>
+        <v>380.0</v>
       </c>
       <c r="I37" s="3">
-        <v>24.3</v>
+        <v>16.62</v>
       </c>
       <c r="J37" s="3">
-        <v>475.7</v>
+        <v>363.38</v>
       </c>
       <c r="K37" t="s">
         <v>15</v>
@@ -2290,16 +2323,16 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="1">
-        <v>88802</v>
+        <v>92648</v>
       </c>
       <c r="B38" s="1">
-        <v>46498</v>
+        <v>45926</v>
       </c>
       <c r="C38" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E38" s="1">
         <v>30</v>
@@ -2311,13 +2344,13 @@
         <v>21</v>
       </c>
       <c r="H38" s="3">
-        <v>140.0</v>
+        <v>150.0</v>
       </c>
       <c r="I38" s="3">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="J38" s="3">
-        <v>137.31</v>
+        <v>147.12</v>
       </c>
       <c r="K38" t="s">
         <v>15</v>
@@ -2325,16 +2358,16 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="1">
-        <v>91829</v>
+        <v>92610</v>
       </c>
       <c r="B39" s="1">
-        <v>46864</v>
+        <v>46498</v>
       </c>
       <c r="C39" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E39" s="1">
         <v>30</v>
@@ -2346,13 +2379,13 @@
         <v>21</v>
       </c>
       <c r="H39" s="3">
-        <v>300.0</v>
+        <v>500.0</v>
       </c>
       <c r="I39" s="3">
-        <v>11.5</v>
+        <v>24.3</v>
       </c>
       <c r="J39" s="3">
-        <v>288.5</v>
+        <v>475.7</v>
       </c>
       <c r="K39" t="s">
         <v>15</v>
@@ -2360,10 +2393,10 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="1">
-        <v>91824</v>
+        <v>88802</v>
       </c>
       <c r="B40" s="1">
-        <v>51024</v>
+        <v>46498</v>
       </c>
       <c r="C40" t="s">
         <v>93</v>
@@ -2378,16 +2411,16 @@
         <v>13</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H40" s="3">
-        <v>220.0</v>
+        <v>140.0</v>
       </c>
       <c r="I40" s="3">
-        <v>6.38</v>
+        <v>2.69</v>
       </c>
       <c r="J40" s="3">
-        <v>213.62</v>
+        <v>137.31</v>
       </c>
       <c r="K40" t="s">
         <v>15</v>
@@ -2395,10 +2428,10 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="1">
-        <v>91844</v>
+        <v>92663</v>
       </c>
       <c r="B41" s="1">
-        <v>56230</v>
+        <v>46864</v>
       </c>
       <c r="C41" t="s">
         <v>95</v>
@@ -2416,13 +2449,13 @@
         <v>21</v>
       </c>
       <c r="H41" s="3">
-        <v>200.0</v>
+        <v>300.0</v>
       </c>
       <c r="I41" s="3">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="J41" s="3">
-        <v>194.9</v>
+        <v>288.5</v>
       </c>
       <c r="K41" t="s">
         <v>15</v>
@@ -2430,10 +2463,10 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="1">
-        <v>91774</v>
+        <v>92659</v>
       </c>
       <c r="B42" s="1">
-        <v>58944</v>
+        <v>51024</v>
       </c>
       <c r="C42" t="s">
         <v>97</v>
@@ -2448,16 +2481,16 @@
         <v>13</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="H42" s="3">
-        <v>470.0</v>
+        <v>220.0</v>
       </c>
       <c r="I42" s="3">
-        <v>22.38</v>
+        <v>6.38</v>
       </c>
       <c r="J42" s="3">
-        <v>447.62</v>
+        <v>213.62</v>
       </c>
       <c r="K42" t="s">
         <v>15</v>
@@ -2465,17 +2498,17 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="1">
-        <v>91776</v>
+        <v>92677</v>
       </c>
       <c r="B43" s="1">
-        <v>59288</v>
+        <v>56230</v>
       </c>
       <c r="C43" t="s">
+        <v>99</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="E43" s="1">
         <v>30</v>
       </c>
@@ -2483,16 +2516,16 @@
         <v>13</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H43" s="3">
-        <v>1480.0</v>
+        <v>200.0</v>
       </c>
       <c r="I43" s="3">
-        <v>88.0</v>
+        <v>5.1</v>
       </c>
       <c r="J43" s="3">
-        <v>1392.0</v>
+        <v>194.9</v>
       </c>
       <c r="K43" t="s">
         <v>15</v>
@@ -2500,16 +2533,16 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="1">
-        <v>91782</v>
+        <v>92597</v>
       </c>
       <c r="B44" s="1">
-        <v>59905</v>
+        <v>58762</v>
       </c>
       <c r="C44" t="s">
+        <v>101</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="E44" s="1">
         <v>30</v>
@@ -2521,13 +2554,13 @@
         <v>18</v>
       </c>
       <c r="H44" s="3">
-        <v>290.0</v>
+        <v>120.0</v>
       </c>
       <c r="I44" s="3">
-        <v>10.86</v>
+        <v>2.3</v>
       </c>
       <c r="J44" s="3">
-        <v>279.14</v>
+        <v>117.7</v>
       </c>
       <c r="K44" t="s">
         <v>15</v>
@@ -2535,34 +2568,34 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="1">
-        <v>91778</v>
+        <v>92620</v>
       </c>
       <c r="B45" s="1">
-        <v>60495</v>
+        <v>58944</v>
       </c>
       <c r="C45" t="s">
+        <v>103</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="E45" s="1">
+        <v>30</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E45" s="1">
-        <v>30</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="H45" s="3">
-        <v>200.0</v>
+        <v>470.0</v>
       </c>
       <c r="I45" s="3">
-        <v>5.1</v>
+        <v>22.38</v>
       </c>
       <c r="J45" s="3">
-        <v>194.9</v>
+        <v>447.62</v>
       </c>
       <c r="K45" t="s">
         <v>15</v>
@@ -2570,10 +2603,10 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="1">
-        <v>91822</v>
+        <v>92622</v>
       </c>
       <c r="B46" s="1">
-        <v>62272</v>
+        <v>59288</v>
       </c>
       <c r="C46" t="s">
         <v>106</v>
@@ -2588,16 +2621,16 @@
         <v>13</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H46" s="3">
-        <v>330.0</v>
+        <v>1480.0</v>
       </c>
       <c r="I46" s="3">
-        <v>13.42</v>
+        <v>88.0</v>
       </c>
       <c r="J46" s="3">
-        <v>316.58</v>
+        <v>1392.0</v>
       </c>
       <c r="K46" t="s">
         <v>15</v>
@@ -2605,10 +2638,10 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="1">
-        <v>91807</v>
+        <v>92589</v>
       </c>
       <c r="B47" s="1">
-        <v>63848</v>
+        <v>59905</v>
       </c>
       <c r="C47" t="s">
         <v>108</v>
@@ -2623,16 +2656,16 @@
         <v>13</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H47" s="3">
-        <v>140.0</v>
+        <v>360.0</v>
       </c>
       <c r="I47" s="3">
-        <v>2.69</v>
+        <v>15.34</v>
       </c>
       <c r="J47" s="3">
-        <v>137.31</v>
+        <v>344.66</v>
       </c>
       <c r="K47" t="s">
         <v>15</v>
@@ -2640,10 +2673,10 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="1">
-        <v>91833</v>
+        <v>92601</v>
       </c>
       <c r="B48" s="1">
-        <v>63902</v>
+        <v>60469</v>
       </c>
       <c r="C48" t="s">
         <v>110</v>
@@ -2658,7 +2691,7 @@
         <v>13</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="H48" s="3">
         <v>150.0</v>
@@ -2675,10 +2708,10 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="1">
-        <v>91842</v>
+        <v>92624</v>
       </c>
       <c r="B49" s="1">
-        <v>65443</v>
+        <v>60495</v>
       </c>
       <c r="C49" t="s">
         <v>112</v>
@@ -2696,13 +2729,13 @@
         <v>21</v>
       </c>
       <c r="H49" s="3">
-        <v>150.0</v>
+        <v>200.0</v>
       </c>
       <c r="I49" s="3">
-        <v>2.88</v>
+        <v>5.1</v>
       </c>
       <c r="J49" s="3">
-        <v>147.12</v>
+        <v>194.9</v>
       </c>
       <c r="K49" t="s">
         <v>15</v>
@@ -2710,10 +2743,10 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="1">
-        <v>91816</v>
+        <v>92590</v>
       </c>
       <c r="B50" s="1">
-        <v>65557</v>
+        <v>62272</v>
       </c>
       <c r="C50" t="s">
         <v>114</v>
@@ -2728,16 +2761,16 @@
         <v>13</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H50" s="3">
-        <v>140.0</v>
+        <v>380.0</v>
       </c>
       <c r="I50" s="3">
-        <v>2.69</v>
+        <v>16.62</v>
       </c>
       <c r="J50" s="3">
-        <v>137.31</v>
+        <v>363.38</v>
       </c>
       <c r="K50" t="s">
         <v>15</v>
@@ -2745,10 +2778,10 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="1">
-        <v>91777</v>
+        <v>92646</v>
       </c>
       <c r="B51" s="1">
-        <v>65868</v>
+        <v>63848</v>
       </c>
       <c r="C51" t="s">
         <v>116</v>
@@ -2763,16 +2796,16 @@
         <v>13</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H51" s="3">
-        <v>280.0</v>
+        <v>140.0</v>
       </c>
       <c r="I51" s="3">
-        <v>10.22</v>
+        <v>2.69</v>
       </c>
       <c r="J51" s="3">
-        <v>269.78</v>
+        <v>137.31</v>
       </c>
       <c r="K51" t="s">
         <v>15</v>
@@ -2780,10 +2813,10 @@
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="1">
-        <v>91780</v>
+        <v>92667</v>
       </c>
       <c r="B52" s="1">
-        <v>68871</v>
+        <v>63902</v>
       </c>
       <c r="C52" t="s">
         <v>118</v>
@@ -2798,16 +2831,16 @@
         <v>13</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="H52" s="3">
-        <v>170.0</v>
+        <v>150.0</v>
       </c>
       <c r="I52" s="3">
-        <v>3.26</v>
+        <v>2.88</v>
       </c>
       <c r="J52" s="3">
-        <v>166.74</v>
+        <v>147.12</v>
       </c>
       <c r="K52" t="s">
         <v>15</v>
@@ -2815,10 +2848,10 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="1">
-        <v>91797</v>
+        <v>92605</v>
       </c>
       <c r="B53" s="1">
-        <v>70487</v>
+        <v>65443</v>
       </c>
       <c r="C53" t="s">
         <v>120</v>
@@ -2833,16 +2866,16 @@
         <v>13</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H53" s="3">
-        <v>350.0</v>
+        <v>200.0</v>
       </c>
       <c r="I53" s="3">
-        <v>14.7</v>
+        <v>5.1</v>
       </c>
       <c r="J53" s="3">
-        <v>335.3</v>
+        <v>194.9</v>
       </c>
       <c r="K53" t="s">
         <v>15</v>
@@ -2850,10 +2883,10 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="1">
-        <v>91798</v>
+        <v>92602</v>
       </c>
       <c r="B54" s="1">
-        <v>86244</v>
+        <v>65557</v>
       </c>
       <c r="C54" t="s">
         <v>122</v>
@@ -2868,16 +2901,16 @@
         <v>13</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H54" s="3">
-        <v>250.0</v>
+        <v>190.0</v>
       </c>
       <c r="I54" s="3">
-        <v>8.3</v>
+        <v>4.46</v>
       </c>
       <c r="J54" s="3">
-        <v>241.7</v>
+        <v>185.54</v>
       </c>
       <c r="K54" t="s">
         <v>15</v>
@@ -2885,10 +2918,10 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="1">
-        <v>91789</v>
+        <v>92623</v>
       </c>
       <c r="B55" s="1">
-        <v>86276</v>
+        <v>65868</v>
       </c>
       <c r="C55" t="s">
         <v>124</v>
@@ -2903,16 +2936,16 @@
         <v>13</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="H55" s="3">
-        <v>370.0</v>
+        <v>280.0</v>
       </c>
       <c r="I55" s="3">
-        <v>15.98</v>
+        <v>10.22</v>
       </c>
       <c r="J55" s="3">
-        <v>354.02</v>
+        <v>269.78</v>
       </c>
       <c r="K55" t="s">
         <v>15</v>
@@ -2920,17 +2953,17 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="1">
-        <v>91821</v>
+        <v>92626</v>
       </c>
       <c r="B56" s="1">
-        <v>103080</v>
+        <v>68871</v>
       </c>
       <c r="C56" t="s">
+        <v>126</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="E56" s="1">
         <v>30</v>
       </c>
@@ -2938,16 +2971,16 @@
         <v>13</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H56" s="3">
-        <v>260.0</v>
+        <v>170.0</v>
       </c>
       <c r="I56" s="3">
-        <v>8.94</v>
+        <v>3.26</v>
       </c>
       <c r="J56" s="3">
-        <v>251.06</v>
+        <v>166.74</v>
       </c>
       <c r="K56" t="s">
         <v>15</v>
@@ -2955,17 +2988,17 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="1">
-        <v>91808</v>
+        <v>92639</v>
       </c>
       <c r="B57" s="1">
-        <v>127349</v>
+        <v>70487</v>
       </c>
       <c r="C57" t="s">
+        <v>128</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="E57" s="1">
         <v>30</v>
       </c>
@@ -2973,16 +3006,16 @@
         <v>13</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H57" s="3">
-        <v>220.0</v>
+        <v>350.0</v>
       </c>
       <c r="I57" s="3">
-        <v>6.38</v>
+        <v>14.7</v>
       </c>
       <c r="J57" s="3">
-        <v>213.62</v>
+        <v>335.3</v>
       </c>
       <c r="K57" t="s">
         <v>15</v>
@@ -2990,17 +3023,17 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="1">
-        <v>91788</v>
+        <v>92603</v>
       </c>
       <c r="B58" s="1">
-        <v>130809</v>
+        <v>75406</v>
       </c>
       <c r="C58" t="s">
+        <v>130</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="E58" s="1">
         <v>30</v>
       </c>
@@ -3008,16 +3041,16 @@
         <v>13</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="H58" s="3">
-        <v>380.0</v>
+        <v>150.0</v>
       </c>
       <c r="I58" s="3">
-        <v>16.62</v>
+        <v>2.88</v>
       </c>
       <c r="J58" s="3">
-        <v>363.38</v>
+        <v>147.12</v>
       </c>
       <c r="K58" t="s">
         <v>15</v>
@@ -3025,17 +3058,17 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="1">
-        <v>91814</v>
+        <v>92640</v>
       </c>
       <c r="B59" s="1">
-        <v>134018</v>
+        <v>86244</v>
       </c>
       <c r="C59" t="s">
+        <v>132</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="E59" s="1">
         <v>30</v>
       </c>
@@ -3043,16 +3076,16 @@
         <v>13</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="H59" s="3">
-        <v>340.0</v>
+        <v>250.0</v>
       </c>
       <c r="I59" s="3">
-        <v>14.06</v>
+        <v>8.3</v>
       </c>
       <c r="J59" s="3">
-        <v>325.94</v>
+        <v>241.7</v>
       </c>
       <c r="K59" t="s">
         <v>15</v>
@@ -3060,34 +3093,34 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="1">
-        <v>91817</v>
+        <v>92586</v>
       </c>
       <c r="B60" s="1">
-        <v>144316</v>
+        <v>86276</v>
       </c>
       <c r="C60" t="s">
+        <v>134</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="E60" s="1">
+        <v>30</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E60" s="1">
-        <v>30</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="H60" s="3">
-        <v>240.0</v>
+        <v>420.0</v>
       </c>
       <c r="I60" s="3">
-        <v>7.66</v>
+        <v>19.18</v>
       </c>
       <c r="J60" s="3">
-        <v>232.34</v>
+        <v>400.82</v>
       </c>
       <c r="K60" t="s">
         <v>15</v>
@@ -3095,10 +3128,10 @@
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="1">
-        <v>91806</v>
+        <v>92658</v>
       </c>
       <c r="B61" s="1">
-        <v>147157</v>
+        <v>103080</v>
       </c>
       <c r="C61" t="s">
         <v>137</v>
@@ -3113,16 +3146,16 @@
         <v>13</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H61" s="3">
-        <v>120.0</v>
+        <v>260.0</v>
       </c>
       <c r="I61" s="3">
-        <v>2.3</v>
+        <v>8.94</v>
       </c>
       <c r="J61" s="3">
-        <v>117.7</v>
+        <v>251.06</v>
       </c>
       <c r="K61" t="s">
         <v>15</v>
@@ -3130,10 +3163,10 @@
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="1">
-        <v>91796</v>
+        <v>92647</v>
       </c>
       <c r="B62" s="1">
-        <v>157471</v>
+        <v>127349</v>
       </c>
       <c r="C62" t="s">
         <v>139</v>
@@ -3148,16 +3181,16 @@
         <v>13</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H62" s="3">
-        <v>200.0</v>
+        <v>220.0</v>
       </c>
       <c r="I62" s="3">
-        <v>5.1</v>
+        <v>6.38</v>
       </c>
       <c r="J62" s="3">
-        <v>194.9</v>
+        <v>213.62</v>
       </c>
       <c r="K62" t="s">
         <v>15</v>
@@ -3165,16 +3198,16 @@
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="1">
-        <v>91800</v>
+        <v>92594</v>
       </c>
       <c r="B63" s="1">
-        <v>161135</v>
+        <v>129078</v>
       </c>
       <c r="C63" t="s">
         <v>141</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E63" s="1">
         <v>30</v>
@@ -3183,16 +3216,16 @@
         <v>13</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="H63" s="3">
-        <v>320.0</v>
+        <v>150.0</v>
       </c>
       <c r="I63" s="3">
-        <v>12.78</v>
+        <v>2.88</v>
       </c>
       <c r="J63" s="3">
-        <v>307.22</v>
+        <v>147.12</v>
       </c>
       <c r="K63" t="s">
         <v>15</v>
@@ -3200,17 +3233,17 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="1">
-        <v>91775</v>
+        <v>92633</v>
       </c>
       <c r="B64" s="1">
-        <v>161167</v>
+        <v>130809</v>
       </c>
       <c r="C64" t="s">
+        <v>142</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D64" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="E64" s="1">
         <v>30</v>
       </c>
@@ -3218,16 +3251,16 @@
         <v>13</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="H64" s="3">
-        <v>1020.0</v>
+        <v>380.0</v>
       </c>
       <c r="I64" s="3">
-        <v>57.58</v>
+        <v>16.62</v>
       </c>
       <c r="J64" s="3">
-        <v>962.42</v>
+        <v>363.38</v>
       </c>
       <c r="K64" t="s">
         <v>15</v>
@@ -3235,16 +3268,16 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="1">
-        <v>91840</v>
+        <v>92653</v>
       </c>
       <c r="B65" s="1">
-        <v>161177</v>
+        <v>134018</v>
       </c>
       <c r="C65" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E65" s="1">
         <v>30</v>
@@ -3253,16 +3286,16 @@
         <v>13</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="H65" s="3">
-        <v>180.0</v>
+        <v>340.0</v>
       </c>
       <c r="I65" s="3">
-        <v>3.82</v>
+        <v>14.06</v>
       </c>
       <c r="J65" s="3">
-        <v>176.18</v>
+        <v>325.94</v>
       </c>
       <c r="K65" t="s">
         <v>15</v>
@@ -3270,16 +3303,16 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="1">
-        <v>91841</v>
+        <v>92654</v>
       </c>
       <c r="B66" s="1">
-        <v>161202</v>
+        <v>144316</v>
       </c>
       <c r="C66" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E66" s="1">
         <v>30</v>
@@ -3288,16 +3321,16 @@
         <v>13</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="H66" s="3">
-        <v>250.0</v>
+        <v>240.0</v>
       </c>
       <c r="I66" s="3">
-        <v>8.3</v>
+        <v>7.66</v>
       </c>
       <c r="J66" s="3">
-        <v>241.7</v>
+        <v>232.34</v>
       </c>
       <c r="K66" t="s">
         <v>15</v>
@@ -3305,16 +3338,16 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="1">
-        <v>91820</v>
+        <v>92645</v>
       </c>
       <c r="B67" s="1">
-        <v>161225</v>
+        <v>147157</v>
       </c>
       <c r="C67" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E67" s="1">
         <v>30</v>
@@ -3323,16 +3356,16 @@
         <v>13</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H67" s="3">
-        <v>200.0</v>
+        <v>120.0</v>
       </c>
       <c r="I67" s="3">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="J67" s="3">
-        <v>194.9</v>
+        <v>117.7</v>
       </c>
       <c r="K67" t="s">
         <v>15</v>
@@ -3340,16 +3373,16 @@
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="1">
-        <v>91848</v>
+        <v>92598</v>
       </c>
       <c r="B68" s="1">
-        <v>161666</v>
+        <v>157471</v>
       </c>
       <c r="C68" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E68" s="1">
         <v>30</v>
@@ -3358,16 +3391,16 @@
         <v>13</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H68" s="3">
-        <v>140.0</v>
+        <v>300.0</v>
       </c>
       <c r="I68" s="3">
-        <v>2.69</v>
+        <v>11.5</v>
       </c>
       <c r="J68" s="3">
-        <v>137.31</v>
+        <v>288.5</v>
       </c>
       <c r="K68" t="s">
         <v>15</v>
@@ -3375,30 +3408,34 @@
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="1">
-        <v>91847</v>
+        <v>92642</v>
       </c>
       <c r="B69" s="1">
-        <v>161783</v>
+        <v>161135</v>
       </c>
       <c r="C69" t="s">
-        <v>154</v>
-      </c>
-      <c r="D69" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>153</v>
+      </c>
       <c r="E69" s="1">
         <v>30</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G69" s="1"/>
+      <c r="G69" s="1" t="s">
+        <v>105</v>
+      </c>
       <c r="H69" s="3">
-        <v>200.0</v>
+        <v>320.0</v>
       </c>
       <c r="I69" s="3">
-        <v>5.1</v>
+        <v>12.78</v>
       </c>
       <c r="J69" s="3">
-        <v>194.9</v>
+        <v>307.22</v>
       </c>
       <c r="K69" t="s">
         <v>15</v>
@@ -3406,34 +3443,34 @@
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="1">
-        <v>91846</v>
+        <v>92621</v>
       </c>
       <c r="B70" s="1">
-        <v>162042</v>
+        <v>161167</v>
       </c>
       <c r="C70" t="s">
+        <v>154</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="E70" s="1">
+        <v>30</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E70" s="1">
-        <v>30</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="H70" s="3">
-        <v>220.0</v>
+        <v>1020.0</v>
       </c>
       <c r="I70" s="3">
-        <v>6.38</v>
+        <v>57.58</v>
       </c>
       <c r="J70" s="3">
-        <v>213.62</v>
+        <v>962.42</v>
       </c>
       <c r="K70" t="s">
         <v>15</v>
@@ -3441,36 +3478,242 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="1">
-        <v>91845</v>
+        <v>92674</v>
       </c>
       <c r="B71" s="1">
-        <v>162077</v>
+        <v>161177</v>
       </c>
       <c r="C71" t="s">
         <v>157</v>
       </c>
       <c r="D71" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E71" s="1">
+        <v>30</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H71" s="3">
+        <v>180.0</v>
+      </c>
+      <c r="I71" s="3">
+        <v>3.82</v>
+      </c>
+      <c r="J71" s="3">
+        <v>176.18</v>
+      </c>
+      <c r="K71" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="1">
+        <v>92675</v>
+      </c>
+      <c r="B72" s="1">
+        <v>161202</v>
+      </c>
+      <c r="C72" t="s">
+        <v>159</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E72" s="1">
+        <v>30</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E71" s="1">
-        <v>30</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G71" s="1" t="s">
+      <c r="H72" s="3">
+        <v>250.0</v>
+      </c>
+      <c r="I72" s="3">
+        <v>8.3</v>
+      </c>
+      <c r="J72" s="3">
+        <v>241.7</v>
+      </c>
+      <c r="K72" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" s="1">
+        <v>92657</v>
+      </c>
+      <c r="B73" s="1">
+        <v>161225</v>
+      </c>
+      <c r="C73" t="s">
+        <v>161</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E73" s="1">
+        <v>30</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H73" s="3">
+        <v>200.0</v>
+      </c>
+      <c r="I73" s="3">
+        <v>5.1</v>
+      </c>
+      <c r="J73" s="3">
+        <v>194.9</v>
+      </c>
+      <c r="K73" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" s="1">
+        <v>92681</v>
+      </c>
+      <c r="B74" s="1">
+        <v>161666</v>
+      </c>
+      <c r="C74" t="s">
+        <v>163</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E74" s="1">
+        <v>30</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H74" s="3">
+        <v>140.0</v>
+      </c>
+      <c r="I74" s="3">
+        <v>2.69</v>
+      </c>
+      <c r="J74" s="3">
+        <v>137.31</v>
+      </c>
+      <c r="K74" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" s="1">
+        <v>92680</v>
+      </c>
+      <c r="B75" s="1">
+        <v>161783</v>
+      </c>
+      <c r="C75" t="s">
+        <v>165</v>
+      </c>
+      <c r="D75" s="2"/>
+      <c r="E75" s="1">
+        <v>30</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" s="1"/>
+      <c r="H75" s="3">
+        <v>200.0</v>
+      </c>
+      <c r="I75" s="3">
+        <v>5.1</v>
+      </c>
+      <c r="J75" s="3">
+        <v>194.9</v>
+      </c>
+      <c r="K75" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" s="1">
+        <v>92679</v>
+      </c>
+      <c r="B76" s="1">
+        <v>162042</v>
+      </c>
+      <c r="C76" t="s">
+        <v>166</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E76" s="1">
+        <v>30</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H71" s="3">
+      <c r="H76" s="3">
+        <v>220.0</v>
+      </c>
+      <c r="I76" s="3">
+        <v>6.38</v>
+      </c>
+      <c r="J76" s="3">
+        <v>213.62</v>
+      </c>
+      <c r="K76" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" s="1">
+        <v>92678</v>
+      </c>
+      <c r="B77" s="1">
+        <v>162077</v>
+      </c>
+      <c r="C77" t="s">
+        <v>168</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E77" s="1">
+        <v>30</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H77" s="3">
         <v>150.0</v>
       </c>
-      <c r="I71" s="3">
+      <c r="I77" s="3">
         <v>2.88</v>
       </c>
-      <c r="J71" s="3">
+      <c r="J77" s="3">
         <v>147.12</v>
       </c>
-      <c r="K71" t="s">
+      <c r="K77" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3512,7 +3755,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>3</v>
@@ -3527,13 +3770,13 @@
         <v>7</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="K1" s="7" t="s">
         <v>9</v>
@@ -3542,21 +3785,21 @@
         <v>10</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="1">
-        <v>91790</v>
+        <v>92634</v>
       </c>
       <c r="B2" s="1">
         <v>15862</v>
       </c>
       <c r="C2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -3583,21 +3826,21 @@
         <v>15</v>
       </c>
       <c r="M2" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1">
-        <v>91773</v>
+        <v>92619</v>
       </c>
       <c r="B3" s="1">
         <v>28826</v>
       </c>
       <c r="C3" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="E3" s="1">
         <v>30</v>
@@ -3624,21 +3867,21 @@
         <v>15</v>
       </c>
       <c r="M3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1">
-        <v>91771</v>
+        <v>92617</v>
       </c>
       <c r="B4" s="1">
         <v>32605</v>
       </c>
       <c r="C4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E4" s="1">
         <v>30</v>
@@ -3665,21 +3908,21 @@
         <v>15</v>
       </c>
       <c r="M4" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1">
-        <v>91825</v>
+        <v>92660</v>
       </c>
       <c r="B5" s="1">
         <v>32614</v>
       </c>
       <c r="C5" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="E5" s="1">
         <v>30</v>
@@ -3706,7 +3949,7 @@
         <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -3747,13 +3990,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>2</v>
@@ -3768,22 +4011,22 @@
         <v>5</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>7</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="O1" s="7" t="s">
         <v>9</v>
@@ -3794,22 +4037,22 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1">
-        <v>91762</v>
+        <v>92609</v>
       </c>
       <c r="B2" s="1">
         <v>80161701</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D2" s="1">
         <v>10859</v>
       </c>
       <c r="E2" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="G2" s="1">
         <v>30</v>
@@ -3844,22 +4087,22 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1">
-        <v>91779</v>
+        <v>92625</v>
       </c>
       <c r="B3" s="1">
         <v>80161701</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D3" s="1">
         <v>17507</v>
       </c>
       <c r="E3" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="G3" s="1">
         <v>30</v>
@@ -3894,22 +4137,22 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1">
-        <v>91766</v>
+        <v>92613</v>
       </c>
       <c r="B4" s="1">
         <v>80161701</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D4" s="1">
         <v>25918</v>
       </c>
       <c r="E4" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="G4" s="1">
         <v>30</v>
@@ -3944,22 +4187,22 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1">
-        <v>91793</v>
+        <v>92637</v>
       </c>
       <c r="B5" s="1">
         <v>80161701</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D5" s="1">
         <v>31622</v>
       </c>
       <c r="E5" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="G5" s="1">
         <v>30</v>
@@ -3994,22 +4237,22 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1">
-        <v>91792</v>
+        <v>92636</v>
       </c>
       <c r="B6" s="1">
         <v>80161701</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D6" s="1">
         <v>31624</v>
       </c>
       <c r="E6" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="G6" s="1">
         <v>30</v>
@@ -4044,22 +4287,22 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1">
-        <v>91787</v>
+        <v>92632</v>
       </c>
       <c r="B7" s="1">
         <v>80161701</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D7" s="1">
         <v>31711</v>
       </c>
       <c r="E7" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="G7" s="1">
         <v>30</v>

--- a/public_html/assets/archivo/corte/40-GASOLINAS/40-GASOLINAS_01-2025_01.xlsx
+++ b/public_html/assets/archivo/corte/40-GASOLINAS/40-GASOLINAS_01-2025_01.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="205">
   <si>
     <t>PAGO</t>
   </si>
@@ -125,6 +125,12 @@
   </si>
   <si>
     <t>012528011651278151</t>
+  </si>
+  <si>
+    <t>MARIA DE LOS ANGELES  CONTRERAS  ALONSO</t>
+  </si>
+  <si>
+    <t>127550013982268911</t>
   </si>
   <si>
     <t>JOSE DE JESUS  VARELA  SANCHEZ</t>
@@ -1010,7 +1016,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="1"/>
@@ -1063,7 +1069,7 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1">
-        <v>92606</v>
+        <v>92702</v>
       </c>
       <c r="B2" s="1">
         <v>3146</v>
@@ -1098,7 +1104,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1">
-        <v>92616</v>
+        <v>92712</v>
       </c>
       <c r="B3" s="1">
         <v>4209</v>
@@ -1133,7 +1139,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1">
-        <v>92635</v>
+        <v>92731</v>
       </c>
       <c r="B4" s="1">
         <v>8272</v>
@@ -1168,7 +1174,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1">
-        <v>92644</v>
+        <v>92741</v>
       </c>
       <c r="B5" s="1">
         <v>11101</v>
@@ -1203,7 +1209,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1">
-        <v>92638</v>
+        <v>92734</v>
       </c>
       <c r="B6" s="1">
         <v>12634</v>
@@ -1238,7 +1244,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1">
-        <v>92650</v>
+        <v>92747</v>
       </c>
       <c r="B7" s="1">
         <v>14975</v>
@@ -1273,7 +1279,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1">
-        <v>92595</v>
+        <v>92691</v>
       </c>
       <c r="B8" s="1">
         <v>17042</v>
@@ -1308,7 +1314,7 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1">
-        <v>92641</v>
+        <v>92737</v>
       </c>
       <c r="B9" s="1">
         <v>25919</v>
@@ -1343,7 +1349,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1">
-        <v>92612</v>
+        <v>92708</v>
       </c>
       <c r="B10" s="1">
         <v>26120</v>
@@ -1378,10 +1384,10 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1">
-        <v>92588</v>
+        <v>92740</v>
       </c>
       <c r="B11" s="1">
-        <v>27736</v>
+        <v>27028</v>
       </c>
       <c r="C11" t="s">
         <v>36</v>
@@ -1399,13 +1405,13 @@
         <v>33</v>
       </c>
       <c r="H11" s="3">
-        <v>240.0</v>
+        <v>130.0</v>
       </c>
       <c r="I11" s="3">
-        <v>7.66</v>
+        <v>2.5</v>
       </c>
       <c r="J11" s="3">
-        <v>232.34</v>
+        <v>127.5</v>
       </c>
       <c r="K11" t="s">
         <v>15</v>
@@ -1413,10 +1419,10 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1">
-        <v>92643</v>
+        <v>92684</v>
       </c>
       <c r="B12" s="1">
-        <v>28458</v>
+        <v>27736</v>
       </c>
       <c r="C12" t="s">
         <v>38</v>
@@ -1431,7 +1437,7 @@
         <v>13</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H12" s="3">
         <v>240.0</v>
@@ -1448,34 +1454,34 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1">
-        <v>92600</v>
+        <v>92739</v>
       </c>
       <c r="B13" s="1">
-        <v>28629</v>
+        <v>28458</v>
       </c>
       <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="1">
+        <v>30</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="1">
-        <v>30</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="H13" s="3">
-        <v>250.0</v>
+        <v>240.0</v>
       </c>
       <c r="I13" s="3">
-        <v>8.3</v>
+        <v>7.66</v>
       </c>
       <c r="J13" s="3">
-        <v>241.7</v>
+        <v>232.34</v>
       </c>
       <c r="K13" t="s">
         <v>15</v>
@@ -1483,10 +1489,10 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1">
-        <v>92615</v>
+        <v>92696</v>
       </c>
       <c r="B14" s="1">
-        <v>30443</v>
+        <v>28629</v>
       </c>
       <c r="C14" t="s">
         <v>43</v>
@@ -1504,13 +1510,13 @@
         <v>18</v>
       </c>
       <c r="H14" s="3">
-        <v>550.0</v>
+        <v>250.0</v>
       </c>
       <c r="I14" s="3">
-        <v>27.5</v>
+        <v>8.3</v>
       </c>
       <c r="J14" s="3">
-        <v>522.5</v>
+        <v>241.7</v>
       </c>
       <c r="K14" t="s">
         <v>15</v>
@@ -1518,10 +1524,10 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1">
-        <v>92611</v>
+        <v>92711</v>
       </c>
       <c r="B15" s="1">
-        <v>31177</v>
+        <v>30443</v>
       </c>
       <c r="C15" t="s">
         <v>45</v>
@@ -1536,16 +1542,16 @@
         <v>13</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H15" s="3">
-        <v>390.0</v>
+        <v>550.0</v>
       </c>
       <c r="I15" s="3">
-        <v>17.26</v>
+        <v>27.5</v>
       </c>
       <c r="J15" s="3">
-        <v>372.74</v>
+        <v>522.5</v>
       </c>
       <c r="K15" t="s">
         <v>15</v>
@@ -1553,10 +1559,10 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1">
-        <v>92649</v>
+        <v>92707</v>
       </c>
       <c r="B16" s="1">
-        <v>31645</v>
+        <v>31177</v>
       </c>
       <c r="C16" t="s">
         <v>47</v>
@@ -1574,13 +1580,13 @@
         <v>21</v>
       </c>
       <c r="H16" s="3">
-        <v>240.0</v>
+        <v>390.0</v>
       </c>
       <c r="I16" s="3">
-        <v>7.66</v>
+        <v>17.26</v>
       </c>
       <c r="J16" s="3">
-        <v>232.34</v>
+        <v>372.74</v>
       </c>
       <c r="K16" t="s">
         <v>15</v>
@@ -1588,10 +1594,10 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1">
-        <v>92631</v>
+        <v>92746</v>
       </c>
       <c r="B17" s="1">
-        <v>31758</v>
+        <v>31645</v>
       </c>
       <c r="C17" t="s">
         <v>49</v>
@@ -1606,16 +1612,16 @@
         <v>13</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H17" s="3">
-        <v>480.0</v>
+        <v>240.0</v>
       </c>
       <c r="I17" s="3">
-        <v>23.02</v>
+        <v>7.66</v>
       </c>
       <c r="J17" s="3">
-        <v>456.98</v>
+        <v>232.34</v>
       </c>
       <c r="K17" t="s">
         <v>15</v>
@@ -1623,10 +1629,10 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1">
-        <v>92599</v>
+        <v>92727</v>
       </c>
       <c r="B18" s="1">
-        <v>31868</v>
+        <v>31758</v>
       </c>
       <c r="C18" t="s">
         <v>51</v>
@@ -1644,13 +1650,13 @@
         <v>33</v>
       </c>
       <c r="H18" s="3">
-        <v>870.0</v>
+        <v>480.0</v>
       </c>
       <c r="I18" s="3">
-        <v>47.98</v>
+        <v>23.02</v>
       </c>
       <c r="J18" s="3">
-        <v>822.02</v>
+        <v>456.98</v>
       </c>
       <c r="K18" t="s">
         <v>15</v>
@@ -1658,10 +1664,10 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="1">
-        <v>92662</v>
+        <v>92695</v>
       </c>
       <c r="B19" s="1">
-        <v>31888</v>
+        <v>31868</v>
       </c>
       <c r="C19" t="s">
         <v>53</v>
@@ -1679,13 +1685,13 @@
         <v>33</v>
       </c>
       <c r="H19" s="3">
-        <v>120.0</v>
+        <v>870.0</v>
       </c>
       <c r="I19" s="3">
-        <v>2.3</v>
+        <v>47.98</v>
       </c>
       <c r="J19" s="3">
-        <v>117.7</v>
+        <v>822.02</v>
       </c>
       <c r="K19" t="s">
         <v>15</v>
@@ -1693,10 +1699,10 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1">
-        <v>92656</v>
+        <v>92759</v>
       </c>
       <c r="B20" s="1">
-        <v>32042</v>
+        <v>31888</v>
       </c>
       <c r="C20" t="s">
         <v>55</v>
@@ -1711,16 +1717,16 @@
         <v>13</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H20" s="3">
-        <v>330.0</v>
+        <v>120.0</v>
       </c>
       <c r="I20" s="3">
-        <v>13.42</v>
+        <v>2.3</v>
       </c>
       <c r="J20" s="3">
-        <v>316.58</v>
+        <v>117.7</v>
       </c>
       <c r="K20" t="s">
         <v>15</v>
@@ -1728,10 +1734,10 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="1">
-        <v>92672</v>
+        <v>92753</v>
       </c>
       <c r="B21" s="1">
-        <v>32228</v>
+        <v>32042</v>
       </c>
       <c r="C21" t="s">
         <v>57</v>
@@ -1746,16 +1752,16 @@
         <v>13</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H21" s="3">
-        <v>800.0</v>
+        <v>330.0</v>
       </c>
       <c r="I21" s="3">
-        <v>43.5</v>
+        <v>13.42</v>
       </c>
       <c r="J21" s="3">
-        <v>756.5</v>
+        <v>316.58</v>
       </c>
       <c r="K21" t="s">
         <v>15</v>
@@ -1763,10 +1769,10 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="1">
-        <v>92665</v>
+        <v>92769</v>
       </c>
       <c r="B22" s="1">
-        <v>32565</v>
+        <v>32228</v>
       </c>
       <c r="C22" t="s">
         <v>59</v>
@@ -1781,16 +1787,16 @@
         <v>13</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H22" s="3">
-        <v>380.0</v>
+        <v>800.0</v>
       </c>
       <c r="I22" s="3">
-        <v>16.62</v>
+        <v>43.5</v>
       </c>
       <c r="J22" s="3">
-        <v>363.38</v>
+        <v>756.5</v>
       </c>
       <c r="K22" t="s">
         <v>15</v>
@@ -1798,10 +1804,10 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="1">
-        <v>92651</v>
+        <v>92762</v>
       </c>
       <c r="B23" s="1">
-        <v>32782</v>
+        <v>32565</v>
       </c>
       <c r="C23" t="s">
         <v>61</v>
@@ -1816,16 +1822,16 @@
         <v>13</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H23" s="3">
-        <v>150.0</v>
+        <v>380.0</v>
       </c>
       <c r="I23" s="3">
-        <v>2.88</v>
+        <v>16.62</v>
       </c>
       <c r="J23" s="3">
-        <v>147.12</v>
+        <v>363.38</v>
       </c>
       <c r="K23" t="s">
         <v>15</v>
@@ -1833,10 +1839,10 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1">
-        <v>92630</v>
+        <v>92748</v>
       </c>
       <c r="B24" s="1">
-        <v>33949</v>
+        <v>32782</v>
       </c>
       <c r="C24" t="s">
         <v>63</v>
@@ -1851,16 +1857,16 @@
         <v>13</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H24" s="3">
-        <v>250.0</v>
+        <v>150.0</v>
       </c>
       <c r="I24" s="3">
-        <v>8.3</v>
+        <v>2.88</v>
       </c>
       <c r="J24" s="3">
-        <v>241.7</v>
+        <v>147.12</v>
       </c>
       <c r="K24" t="s">
         <v>15</v>
@@ -1868,10 +1874,10 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="1">
-        <v>92629</v>
+        <v>92726</v>
       </c>
       <c r="B25" s="1">
-        <v>34105</v>
+        <v>33949</v>
       </c>
       <c r="C25" t="s">
         <v>65</v>
@@ -1886,16 +1892,16 @@
         <v>13</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H25" s="3">
-        <v>300.0</v>
+        <v>250.0</v>
       </c>
       <c r="I25" s="3">
-        <v>11.5</v>
+        <v>8.3</v>
       </c>
       <c r="J25" s="3">
-        <v>288.5</v>
+        <v>241.7</v>
       </c>
       <c r="K25" t="s">
         <v>15</v>
@@ -1903,10 +1909,10 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1">
-        <v>92614</v>
+        <v>92725</v>
       </c>
       <c r="B26" s="1">
-        <v>35957</v>
+        <v>34105</v>
       </c>
       <c r="C26" t="s">
         <v>67</v>
@@ -1921,16 +1927,16 @@
         <v>13</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H26" s="3">
-        <v>440.0</v>
+        <v>300.0</v>
       </c>
       <c r="I26" s="3">
-        <v>20.46</v>
+        <v>11.5</v>
       </c>
       <c r="J26" s="3">
-        <v>419.54</v>
+        <v>288.5</v>
       </c>
       <c r="K26" t="s">
         <v>15</v>
@@ -1938,10 +1944,10 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1">
-        <v>92587</v>
+        <v>92710</v>
       </c>
       <c r="B27" s="1">
-        <v>37206</v>
+        <v>35957</v>
       </c>
       <c r="C27" t="s">
         <v>69</v>
@@ -1956,16 +1962,16 @@
         <v>13</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H27" s="3">
-        <v>250.0</v>
+        <v>440.0</v>
       </c>
       <c r="I27" s="3">
-        <v>8.3</v>
+        <v>20.46</v>
       </c>
       <c r="J27" s="3">
-        <v>241.7</v>
+        <v>419.54</v>
       </c>
       <c r="K27" t="s">
         <v>15</v>
@@ -1973,10 +1979,10 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="1">
-        <v>92596</v>
+        <v>92683</v>
       </c>
       <c r="B28" s="1">
-        <v>39687</v>
+        <v>37206</v>
       </c>
       <c r="C28" t="s">
         <v>71</v>
@@ -1991,16 +1997,16 @@
         <v>13</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H28" s="3">
-        <v>170.0</v>
+        <v>250.0</v>
       </c>
       <c r="I28" s="3">
-        <v>3.26</v>
+        <v>8.3</v>
       </c>
       <c r="J28" s="3">
-        <v>166.74</v>
+        <v>241.7</v>
       </c>
       <c r="K28" t="s">
         <v>15</v>
@@ -2008,10 +2014,10 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="1">
-        <v>92593</v>
+        <v>92692</v>
       </c>
       <c r="B29" s="1">
-        <v>41172</v>
+        <v>39687</v>
       </c>
       <c r="C29" t="s">
         <v>73</v>
@@ -2029,13 +2035,13 @@
         <v>18</v>
       </c>
       <c r="H29" s="3">
-        <v>230.0</v>
+        <v>170.0</v>
       </c>
       <c r="I29" s="3">
-        <v>7.02</v>
+        <v>3.26</v>
       </c>
       <c r="J29" s="3">
-        <v>222.98</v>
+        <v>166.74</v>
       </c>
       <c r="K29" t="s">
         <v>15</v>
@@ -2043,10 +2049,10 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1">
-        <v>92592</v>
+        <v>92689</v>
       </c>
       <c r="B30" s="1">
-        <v>41428</v>
+        <v>41172</v>
       </c>
       <c r="C30" t="s">
         <v>75</v>
@@ -2064,13 +2070,13 @@
         <v>18</v>
       </c>
       <c r="H30" s="3">
-        <v>120.0</v>
+        <v>230.0</v>
       </c>
       <c r="I30" s="3">
-        <v>2.3</v>
+        <v>7.02</v>
       </c>
       <c r="J30" s="3">
-        <v>117.7</v>
+        <v>222.98</v>
       </c>
       <c r="K30" t="s">
         <v>15</v>
@@ -2078,10 +2084,10 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="1">
-        <v>92618</v>
+        <v>92688</v>
       </c>
       <c r="B31" s="1">
-        <v>41929</v>
+        <v>41428</v>
       </c>
       <c r="C31" t="s">
         <v>77</v>
@@ -2099,13 +2105,13 @@
         <v>18</v>
       </c>
       <c r="H31" s="3">
-        <v>740.0</v>
+        <v>120.0</v>
       </c>
       <c r="I31" s="3">
-        <v>39.66</v>
+        <v>2.3</v>
       </c>
       <c r="J31" s="3">
-        <v>700.34</v>
+        <v>117.7</v>
       </c>
       <c r="K31" t="s">
         <v>15</v>
@@ -2113,10 +2119,10 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="1">
-        <v>92604</v>
+        <v>92714</v>
       </c>
       <c r="B32" s="1">
-        <v>42170</v>
+        <v>41929</v>
       </c>
       <c r="C32" t="s">
         <v>79</v>
@@ -2134,13 +2140,13 @@
         <v>18</v>
       </c>
       <c r="H32" s="3">
-        <v>420.0</v>
+        <v>740.0</v>
       </c>
       <c r="I32" s="3">
-        <v>19.18</v>
+        <v>39.66</v>
       </c>
       <c r="J32" s="3">
-        <v>400.82</v>
+        <v>700.34</v>
       </c>
       <c r="K32" t="s">
         <v>15</v>
@@ -2148,10 +2154,10 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="1">
-        <v>92664</v>
+        <v>92700</v>
       </c>
       <c r="B33" s="1">
-        <v>42575</v>
+        <v>42170</v>
       </c>
       <c r="C33" t="s">
         <v>81</v>
@@ -2166,16 +2172,16 @@
         <v>13</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H33" s="3">
-        <v>620.0</v>
+        <v>420.0</v>
       </c>
       <c r="I33" s="3">
-        <v>31.98</v>
+        <v>19.18</v>
       </c>
       <c r="J33" s="3">
-        <v>588.02</v>
+        <v>400.82</v>
       </c>
       <c r="K33" t="s">
         <v>15</v>
@@ -2183,10 +2189,10 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="1">
-        <v>92668</v>
+        <v>92761</v>
       </c>
       <c r="B34" s="1">
-        <v>42628</v>
+        <v>42575</v>
       </c>
       <c r="C34" t="s">
         <v>83</v>
@@ -2201,16 +2207,16 @@
         <v>13</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H34" s="3">
-        <v>720.0</v>
+        <v>620.0</v>
       </c>
       <c r="I34" s="3">
-        <v>38.38</v>
+        <v>31.98</v>
       </c>
       <c r="J34" s="3">
-        <v>681.62</v>
+        <v>588.02</v>
       </c>
       <c r="K34" t="s">
         <v>15</v>
@@ -2218,10 +2224,10 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="1">
-        <v>92670</v>
+        <v>92765</v>
       </c>
       <c r="B35" s="1">
-        <v>43119</v>
+        <v>42628</v>
       </c>
       <c r="C35" t="s">
         <v>85</v>
@@ -2236,16 +2242,16 @@
         <v>13</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H35" s="3">
-        <v>150.0</v>
+        <v>720.0</v>
       </c>
       <c r="I35" s="3">
-        <v>2.88</v>
+        <v>38.38</v>
       </c>
       <c r="J35" s="3">
-        <v>147.12</v>
+        <v>681.62</v>
       </c>
       <c r="K35" t="s">
         <v>15</v>
@@ -2253,10 +2259,10 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="1">
-        <v>92652</v>
+        <v>92767</v>
       </c>
       <c r="B36" s="1">
-        <v>44798</v>
+        <v>43119</v>
       </c>
       <c r="C36" t="s">
         <v>87</v>
@@ -2271,16 +2277,16 @@
         <v>13</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H36" s="3">
-        <v>250.0</v>
+        <v>150.0</v>
       </c>
       <c r="I36" s="3">
-        <v>8.3</v>
+        <v>2.88</v>
       </c>
       <c r="J36" s="3">
-        <v>241.7</v>
+        <v>147.12</v>
       </c>
       <c r="K36" t="s">
         <v>15</v>
@@ -2288,10 +2294,10 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="1">
-        <v>92628</v>
+        <v>92749</v>
       </c>
       <c r="B37" s="1">
-        <v>45670</v>
+        <v>44798</v>
       </c>
       <c r="C37" t="s">
         <v>89</v>
@@ -2309,13 +2315,13 @@
         <v>18</v>
       </c>
       <c r="H37" s="3">
-        <v>380.0</v>
+        <v>250.0</v>
       </c>
       <c r="I37" s="3">
-        <v>16.62</v>
+        <v>8.3</v>
       </c>
       <c r="J37" s="3">
-        <v>363.38</v>
+        <v>241.7</v>
       </c>
       <c r="K37" t="s">
         <v>15</v>
@@ -2323,10 +2329,10 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="1">
-        <v>92648</v>
+        <v>92724</v>
       </c>
       <c r="B38" s="1">
-        <v>45926</v>
+        <v>45670</v>
       </c>
       <c r="C38" t="s">
         <v>91</v>
@@ -2341,16 +2347,16 @@
         <v>13</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H38" s="3">
-        <v>150.0</v>
+        <v>380.0</v>
       </c>
       <c r="I38" s="3">
-        <v>2.88</v>
+        <v>16.62</v>
       </c>
       <c r="J38" s="3">
-        <v>147.12</v>
+        <v>363.38</v>
       </c>
       <c r="K38" t="s">
         <v>15</v>
@@ -2358,10 +2364,10 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="1">
-        <v>92610</v>
+        <v>92745</v>
       </c>
       <c r="B39" s="1">
-        <v>46498</v>
+        <v>45926</v>
       </c>
       <c r="C39" t="s">
         <v>93</v>
@@ -2379,13 +2385,13 @@
         <v>21</v>
       </c>
       <c r="H39" s="3">
-        <v>500.0</v>
+        <v>150.0</v>
       </c>
       <c r="I39" s="3">
-        <v>24.3</v>
+        <v>2.88</v>
       </c>
       <c r="J39" s="3">
-        <v>475.7</v>
+        <v>147.12</v>
       </c>
       <c r="K39" t="s">
         <v>15</v>
@@ -2393,16 +2399,16 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="1">
-        <v>88802</v>
+        <v>92706</v>
       </c>
       <c r="B40" s="1">
         <v>46498</v>
       </c>
       <c r="C40" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E40" s="1">
         <v>30</v>
@@ -2414,13 +2420,13 @@
         <v>21</v>
       </c>
       <c r="H40" s="3">
-        <v>140.0</v>
+        <v>500.0</v>
       </c>
       <c r="I40" s="3">
-        <v>2.69</v>
+        <v>24.3</v>
       </c>
       <c r="J40" s="3">
-        <v>137.31</v>
+        <v>475.7</v>
       </c>
       <c r="K40" t="s">
         <v>15</v>
@@ -2428,10 +2434,10 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="1">
-        <v>92663</v>
+        <v>88802</v>
       </c>
       <c r="B41" s="1">
-        <v>46864</v>
+        <v>46498</v>
       </c>
       <c r="C41" t="s">
         <v>95</v>
@@ -2449,13 +2455,13 @@
         <v>21</v>
       </c>
       <c r="H41" s="3">
-        <v>300.0</v>
+        <v>140.0</v>
       </c>
       <c r="I41" s="3">
-        <v>11.5</v>
+        <v>2.69</v>
       </c>
       <c r="J41" s="3">
-        <v>288.5</v>
+        <v>137.31</v>
       </c>
       <c r="K41" t="s">
         <v>15</v>
@@ -2463,10 +2469,10 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="1">
-        <v>92659</v>
+        <v>92760</v>
       </c>
       <c r="B42" s="1">
-        <v>51024</v>
+        <v>46864</v>
       </c>
       <c r="C42" t="s">
         <v>97</v>
@@ -2481,16 +2487,16 @@
         <v>13</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H42" s="3">
-        <v>220.0</v>
+        <v>300.0</v>
       </c>
       <c r="I42" s="3">
-        <v>6.38</v>
+        <v>11.5</v>
       </c>
       <c r="J42" s="3">
-        <v>213.62</v>
+        <v>288.5</v>
       </c>
       <c r="K42" t="s">
         <v>15</v>
@@ -2498,10 +2504,10 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="1">
-        <v>92677</v>
+        <v>92756</v>
       </c>
       <c r="B43" s="1">
-        <v>56230</v>
+        <v>51024</v>
       </c>
       <c r="C43" t="s">
         <v>99</v>
@@ -2516,16 +2522,16 @@
         <v>13</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H43" s="3">
-        <v>200.0</v>
+        <v>220.0</v>
       </c>
       <c r="I43" s="3">
-        <v>5.1</v>
+        <v>6.38</v>
       </c>
       <c r="J43" s="3">
-        <v>194.9</v>
+        <v>213.62</v>
       </c>
       <c r="K43" t="s">
         <v>15</v>
@@ -2533,10 +2539,10 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="1">
-        <v>92597</v>
+        <v>92774</v>
       </c>
       <c r="B44" s="1">
-        <v>58762</v>
+        <v>56230</v>
       </c>
       <c r="C44" t="s">
         <v>101</v>
@@ -2551,16 +2557,16 @@
         <v>13</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H44" s="3">
-        <v>120.0</v>
+        <v>200.0</v>
       </c>
       <c r="I44" s="3">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="J44" s="3">
-        <v>117.7</v>
+        <v>194.9</v>
       </c>
       <c r="K44" t="s">
         <v>15</v>
@@ -2568,10 +2574,10 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="1">
-        <v>92620</v>
+        <v>92693</v>
       </c>
       <c r="B45" s="1">
-        <v>58944</v>
+        <v>58762</v>
       </c>
       <c r="C45" t="s">
         <v>103</v>
@@ -2586,16 +2592,16 @@
         <v>13</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="H45" s="3">
-        <v>470.0</v>
+        <v>120.0</v>
       </c>
       <c r="I45" s="3">
-        <v>22.38</v>
+        <v>2.3</v>
       </c>
       <c r="J45" s="3">
-        <v>447.62</v>
+        <v>117.7</v>
       </c>
       <c r="K45" t="s">
         <v>15</v>
@@ -2603,34 +2609,34 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="1">
-        <v>92622</v>
+        <v>92716</v>
       </c>
       <c r="B46" s="1">
-        <v>59288</v>
+        <v>58944</v>
       </c>
       <c r="C46" t="s">
+        <v>105</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="E46" s="1">
+        <v>30</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E46" s="1">
-        <v>30</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="H46" s="3">
-        <v>1480.0</v>
+        <v>470.0</v>
       </c>
       <c r="I46" s="3">
-        <v>88.0</v>
+        <v>22.38</v>
       </c>
       <c r="J46" s="3">
-        <v>1392.0</v>
+        <v>447.62</v>
       </c>
       <c r="K46" t="s">
         <v>15</v>
@@ -2638,10 +2644,10 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="1">
-        <v>92589</v>
+        <v>92718</v>
       </c>
       <c r="B47" s="1">
-        <v>59905</v>
+        <v>59288</v>
       </c>
       <c r="C47" t="s">
         <v>108</v>
@@ -2659,13 +2665,13 @@
         <v>18</v>
       </c>
       <c r="H47" s="3">
-        <v>360.0</v>
+        <v>1480.0</v>
       </c>
       <c r="I47" s="3">
-        <v>15.34</v>
+        <v>88.0</v>
       </c>
       <c r="J47" s="3">
-        <v>344.66</v>
+        <v>1392.0</v>
       </c>
       <c r="K47" t="s">
         <v>15</v>
@@ -2673,10 +2679,10 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="1">
-        <v>92601</v>
+        <v>92685</v>
       </c>
       <c r="B48" s="1">
-        <v>60469</v>
+        <v>59905</v>
       </c>
       <c r="C48" t="s">
         <v>110</v>
@@ -2691,16 +2697,16 @@
         <v>13</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H48" s="3">
-        <v>150.0</v>
+        <v>360.0</v>
       </c>
       <c r="I48" s="3">
-        <v>2.88</v>
+        <v>15.34</v>
       </c>
       <c r="J48" s="3">
-        <v>147.12</v>
+        <v>344.66</v>
       </c>
       <c r="K48" t="s">
         <v>15</v>
@@ -2708,10 +2714,10 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="1">
-        <v>92624</v>
+        <v>92697</v>
       </c>
       <c r="B49" s="1">
-        <v>60495</v>
+        <v>60469</v>
       </c>
       <c r="C49" t="s">
         <v>112</v>
@@ -2726,16 +2732,16 @@
         <v>13</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H49" s="3">
-        <v>200.0</v>
+        <v>150.0</v>
       </c>
       <c r="I49" s="3">
-        <v>5.1</v>
+        <v>2.88</v>
       </c>
       <c r="J49" s="3">
-        <v>194.9</v>
+        <v>147.12</v>
       </c>
       <c r="K49" t="s">
         <v>15</v>
@@ -2743,10 +2749,10 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="1">
-        <v>92590</v>
+        <v>92720</v>
       </c>
       <c r="B50" s="1">
-        <v>62272</v>
+        <v>60495</v>
       </c>
       <c r="C50" t="s">
         <v>114</v>
@@ -2761,16 +2767,16 @@
         <v>13</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H50" s="3">
-        <v>380.0</v>
+        <v>200.0</v>
       </c>
       <c r="I50" s="3">
-        <v>16.62</v>
+        <v>5.1</v>
       </c>
       <c r="J50" s="3">
-        <v>363.38</v>
+        <v>194.9</v>
       </c>
       <c r="K50" t="s">
         <v>15</v>
@@ -2778,10 +2784,10 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="1">
-        <v>92646</v>
+        <v>92686</v>
       </c>
       <c r="B51" s="1">
-        <v>63848</v>
+        <v>62272</v>
       </c>
       <c r="C51" t="s">
         <v>116</v>
@@ -2796,16 +2802,16 @@
         <v>13</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H51" s="3">
-        <v>140.0</v>
+        <v>380.0</v>
       </c>
       <c r="I51" s="3">
-        <v>2.69</v>
+        <v>16.62</v>
       </c>
       <c r="J51" s="3">
-        <v>137.31</v>
+        <v>363.38</v>
       </c>
       <c r="K51" t="s">
         <v>15</v>
@@ -2813,10 +2819,10 @@
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="1">
-        <v>92667</v>
+        <v>92743</v>
       </c>
       <c r="B52" s="1">
-        <v>63902</v>
+        <v>63848</v>
       </c>
       <c r="C52" t="s">
         <v>118</v>
@@ -2831,16 +2837,16 @@
         <v>13</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>105</v>
+        <v>24</v>
       </c>
       <c r="H52" s="3">
-        <v>150.0</v>
+        <v>140.0</v>
       </c>
       <c r="I52" s="3">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="J52" s="3">
-        <v>147.12</v>
+        <v>137.31</v>
       </c>
       <c r="K52" t="s">
         <v>15</v>
@@ -2848,10 +2854,10 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="1">
-        <v>92605</v>
+        <v>92764</v>
       </c>
       <c r="B53" s="1">
-        <v>65443</v>
+        <v>63902</v>
       </c>
       <c r="C53" t="s">
         <v>120</v>
@@ -2866,16 +2872,16 @@
         <v>13</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="H53" s="3">
-        <v>200.0</v>
+        <v>150.0</v>
       </c>
       <c r="I53" s="3">
-        <v>5.1</v>
+        <v>2.88</v>
       </c>
       <c r="J53" s="3">
-        <v>194.9</v>
+        <v>147.12</v>
       </c>
       <c r="K53" t="s">
         <v>15</v>
@@ -2883,10 +2889,10 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="1">
-        <v>92602</v>
+        <v>92701</v>
       </c>
       <c r="B54" s="1">
-        <v>65557</v>
+        <v>65443</v>
       </c>
       <c r="C54" t="s">
         <v>122</v>
@@ -2901,16 +2907,16 @@
         <v>13</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H54" s="3">
-        <v>190.0</v>
+        <v>200.0</v>
       </c>
       <c r="I54" s="3">
-        <v>4.46</v>
+        <v>5.1</v>
       </c>
       <c r="J54" s="3">
-        <v>185.54</v>
+        <v>194.9</v>
       </c>
       <c r="K54" t="s">
         <v>15</v>
@@ -2918,10 +2924,10 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="1">
-        <v>92623</v>
+        <v>92698</v>
       </c>
       <c r="B55" s="1">
-        <v>65868</v>
+        <v>65557</v>
       </c>
       <c r="C55" t="s">
         <v>124</v>
@@ -2936,16 +2942,16 @@
         <v>13</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H55" s="3">
-        <v>280.0</v>
+        <v>190.0</v>
       </c>
       <c r="I55" s="3">
-        <v>10.22</v>
+        <v>4.46</v>
       </c>
       <c r="J55" s="3">
-        <v>269.78</v>
+        <v>185.54</v>
       </c>
       <c r="K55" t="s">
         <v>15</v>
@@ -2953,10 +2959,10 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="1">
-        <v>92626</v>
+        <v>92719</v>
       </c>
       <c r="B56" s="1">
-        <v>68871</v>
+        <v>65868</v>
       </c>
       <c r="C56" t="s">
         <v>126</v>
@@ -2974,13 +2980,13 @@
         <v>21</v>
       </c>
       <c r="H56" s="3">
-        <v>170.0</v>
+        <v>280.0</v>
       </c>
       <c r="I56" s="3">
-        <v>3.26</v>
+        <v>10.22</v>
       </c>
       <c r="J56" s="3">
-        <v>166.74</v>
+        <v>269.78</v>
       </c>
       <c r="K56" t="s">
         <v>15</v>
@@ -2988,10 +2994,10 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="1">
-        <v>92639</v>
+        <v>92722</v>
       </c>
       <c r="B57" s="1">
-        <v>70487</v>
+        <v>68871</v>
       </c>
       <c r="C57" t="s">
         <v>128</v>
@@ -3006,16 +3012,16 @@
         <v>13</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H57" s="3">
-        <v>350.0</v>
+        <v>170.0</v>
       </c>
       <c r="I57" s="3">
-        <v>14.7</v>
+        <v>3.26</v>
       </c>
       <c r="J57" s="3">
-        <v>335.3</v>
+        <v>166.74</v>
       </c>
       <c r="K57" t="s">
         <v>15</v>
@@ -3023,10 +3029,10 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="1">
-        <v>92603</v>
+        <v>92735</v>
       </c>
       <c r="B58" s="1">
-        <v>75406</v>
+        <v>70487</v>
       </c>
       <c r="C58" t="s">
         <v>130</v>
@@ -3041,16 +3047,16 @@
         <v>13</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="H58" s="3">
-        <v>150.0</v>
+        <v>350.0</v>
       </c>
       <c r="I58" s="3">
-        <v>2.88</v>
+        <v>14.7</v>
       </c>
       <c r="J58" s="3">
-        <v>147.12</v>
+        <v>335.3</v>
       </c>
       <c r="K58" t="s">
         <v>15</v>
@@ -3058,10 +3064,10 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="1">
-        <v>92640</v>
+        <v>92699</v>
       </c>
       <c r="B59" s="1">
-        <v>86244</v>
+        <v>75406</v>
       </c>
       <c r="C59" t="s">
         <v>132</v>
@@ -3076,16 +3082,16 @@
         <v>13</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="H59" s="3">
-        <v>250.0</v>
+        <v>150.0</v>
       </c>
       <c r="I59" s="3">
-        <v>8.3</v>
+        <v>2.88</v>
       </c>
       <c r="J59" s="3">
-        <v>241.7</v>
+        <v>147.12</v>
       </c>
       <c r="K59" t="s">
         <v>15</v>
@@ -3093,10 +3099,10 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="1">
-        <v>92586</v>
+        <v>92736</v>
       </c>
       <c r="B60" s="1">
-        <v>86276</v>
+        <v>86244</v>
       </c>
       <c r="C60" t="s">
         <v>134</v>
@@ -3111,16 +3117,16 @@
         <v>13</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="H60" s="3">
-        <v>420.0</v>
+        <v>250.0</v>
       </c>
       <c r="I60" s="3">
-        <v>19.18</v>
+        <v>8.3</v>
       </c>
       <c r="J60" s="3">
-        <v>400.82</v>
+        <v>241.7</v>
       </c>
       <c r="K60" t="s">
         <v>15</v>
@@ -3128,34 +3134,34 @@
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="1">
-        <v>92658</v>
+        <v>92682</v>
       </c>
       <c r="B61" s="1">
-        <v>103080</v>
+        <v>86276</v>
       </c>
       <c r="C61" t="s">
+        <v>136</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="E61" s="1">
+        <v>30</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E61" s="1">
-        <v>30</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="H61" s="3">
-        <v>260.0</v>
+        <v>420.0</v>
       </c>
       <c r="I61" s="3">
-        <v>8.94</v>
+        <v>19.18</v>
       </c>
       <c r="J61" s="3">
-        <v>251.06</v>
+        <v>400.82</v>
       </c>
       <c r="K61" t="s">
         <v>15</v>
@@ -3163,10 +3169,10 @@
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="1">
-        <v>92647</v>
+        <v>92755</v>
       </c>
       <c r="B62" s="1">
-        <v>127349</v>
+        <v>103080</v>
       </c>
       <c r="C62" t="s">
         <v>139</v>
@@ -3181,16 +3187,16 @@
         <v>13</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H62" s="3">
-        <v>220.0</v>
+        <v>260.0</v>
       </c>
       <c r="I62" s="3">
-        <v>6.38</v>
+        <v>8.94</v>
       </c>
       <c r="J62" s="3">
-        <v>213.62</v>
+        <v>251.06</v>
       </c>
       <c r="K62" t="s">
         <v>15</v>
@@ -3198,16 +3204,16 @@
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="1">
-        <v>92594</v>
+        <v>92744</v>
       </c>
       <c r="B63" s="1">
-        <v>129078</v>
+        <v>127349</v>
       </c>
       <c r="C63" t="s">
         <v>141</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E63" s="1">
         <v>30</v>
@@ -3219,13 +3225,13 @@
         <v>21</v>
       </c>
       <c r="H63" s="3">
-        <v>150.0</v>
+        <v>220.0</v>
       </c>
       <c r="I63" s="3">
-        <v>2.88</v>
+        <v>6.38</v>
       </c>
       <c r="J63" s="3">
-        <v>147.12</v>
+        <v>213.62</v>
       </c>
       <c r="K63" t="s">
         <v>15</v>
@@ -3233,17 +3239,17 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="1">
-        <v>92633</v>
+        <v>92690</v>
       </c>
       <c r="B64" s="1">
-        <v>130809</v>
+        <v>129078</v>
       </c>
       <c r="C64" t="s">
+        <v>143</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D64" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="E64" s="1">
         <v>30</v>
       </c>
@@ -3251,16 +3257,16 @@
         <v>13</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="H64" s="3">
-        <v>380.0</v>
+        <v>150.0</v>
       </c>
       <c r="I64" s="3">
-        <v>16.62</v>
+        <v>2.88</v>
       </c>
       <c r="J64" s="3">
-        <v>363.38</v>
+        <v>147.12</v>
       </c>
       <c r="K64" t="s">
         <v>15</v>
@@ -3268,10 +3274,10 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="1">
-        <v>92653</v>
+        <v>92729</v>
       </c>
       <c r="B65" s="1">
-        <v>134018</v>
+        <v>130809</v>
       </c>
       <c r="C65" t="s">
         <v>144</v>
@@ -3286,16 +3292,16 @@
         <v>13</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H65" s="3">
-        <v>340.0</v>
+        <v>380.0</v>
       </c>
       <c r="I65" s="3">
-        <v>14.06</v>
+        <v>16.62</v>
       </c>
       <c r="J65" s="3">
-        <v>325.94</v>
+        <v>363.38</v>
       </c>
       <c r="K65" t="s">
         <v>15</v>
@@ -3303,10 +3309,10 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="1">
-        <v>92654</v>
+        <v>92750</v>
       </c>
       <c r="B66" s="1">
-        <v>144316</v>
+        <v>134018</v>
       </c>
       <c r="C66" t="s">
         <v>146</v>
@@ -3321,16 +3327,16 @@
         <v>13</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H66" s="3">
-        <v>240.0</v>
+        <v>340.0</v>
       </c>
       <c r="I66" s="3">
-        <v>7.66</v>
+        <v>14.06</v>
       </c>
       <c r="J66" s="3">
-        <v>232.34</v>
+        <v>325.94</v>
       </c>
       <c r="K66" t="s">
         <v>15</v>
@@ -3338,10 +3344,10 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="1">
-        <v>92645</v>
+        <v>92751</v>
       </c>
       <c r="B67" s="1">
-        <v>147157</v>
+        <v>144316</v>
       </c>
       <c r="C67" t="s">
         <v>148</v>
@@ -3356,16 +3362,16 @@
         <v>13</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="H67" s="3">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="I67" s="3">
-        <v>2.3</v>
+        <v>7.66</v>
       </c>
       <c r="J67" s="3">
-        <v>117.7</v>
+        <v>232.34</v>
       </c>
       <c r="K67" t="s">
         <v>15</v>
@@ -3373,10 +3379,10 @@
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="1">
-        <v>92598</v>
+        <v>92742</v>
       </c>
       <c r="B68" s="1">
-        <v>157471</v>
+        <v>147157</v>
       </c>
       <c r="C68" t="s">
         <v>150</v>
@@ -3391,16 +3397,16 @@
         <v>13</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H68" s="3">
-        <v>300.0</v>
+        <v>120.0</v>
       </c>
       <c r="I68" s="3">
-        <v>11.5</v>
+        <v>2.3</v>
       </c>
       <c r="J68" s="3">
-        <v>288.5</v>
+        <v>117.7</v>
       </c>
       <c r="K68" t="s">
         <v>15</v>
@@ -3408,10 +3414,10 @@
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="1">
-        <v>92642</v>
+        <v>92694</v>
       </c>
       <c r="B69" s="1">
-        <v>161135</v>
+        <v>157471</v>
       </c>
       <c r="C69" t="s">
         <v>152</v>
@@ -3426,16 +3432,16 @@
         <v>13</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="H69" s="3">
-        <v>320.0</v>
+        <v>300.0</v>
       </c>
       <c r="I69" s="3">
-        <v>12.78</v>
+        <v>11.5</v>
       </c>
       <c r="J69" s="3">
-        <v>307.22</v>
+        <v>288.5</v>
       </c>
       <c r="K69" t="s">
         <v>15</v>
@@ -3443,10 +3449,10 @@
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="1">
-        <v>92621</v>
+        <v>92738</v>
       </c>
       <c r="B70" s="1">
-        <v>161167</v>
+        <v>161135</v>
       </c>
       <c r="C70" t="s">
         <v>154</v>
@@ -3461,16 +3467,16 @@
         <v>13</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="H70" s="3">
-        <v>1020.0</v>
+        <v>320.0</v>
       </c>
       <c r="I70" s="3">
-        <v>57.58</v>
+        <v>12.78</v>
       </c>
       <c r="J70" s="3">
-        <v>962.42</v>
+        <v>307.22</v>
       </c>
       <c r="K70" t="s">
         <v>15</v>
@@ -3478,34 +3484,34 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="1">
-        <v>92674</v>
+        <v>92717</v>
       </c>
       <c r="B71" s="1">
-        <v>161177</v>
+        <v>161167</v>
       </c>
       <c r="C71" t="s">
+        <v>156</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="E71" s="1">
+        <v>30</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E71" s="1">
-        <v>30</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="H71" s="3">
-        <v>180.0</v>
+        <v>1020.0</v>
       </c>
       <c r="I71" s="3">
-        <v>3.82</v>
+        <v>57.58</v>
       </c>
       <c r="J71" s="3">
-        <v>176.18</v>
+        <v>962.42</v>
       </c>
       <c r="K71" t="s">
         <v>15</v>
@@ -3513,10 +3519,10 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="1">
-        <v>92675</v>
+        <v>92771</v>
       </c>
       <c r="B72" s="1">
-        <v>161202</v>
+        <v>161177</v>
       </c>
       <c r="C72" t="s">
         <v>159</v>
@@ -3531,16 +3537,16 @@
         <v>13</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>156</v>
+        <v>18</v>
       </c>
       <c r="H72" s="3">
-        <v>250.0</v>
+        <v>180.0</v>
       </c>
       <c r="I72" s="3">
-        <v>8.3</v>
+        <v>3.82</v>
       </c>
       <c r="J72" s="3">
-        <v>241.7</v>
+        <v>176.18</v>
       </c>
       <c r="K72" t="s">
         <v>15</v>
@@ -3548,10 +3554,10 @@
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="1">
-        <v>92657</v>
+        <v>92772</v>
       </c>
       <c r="B73" s="1">
-        <v>161225</v>
+        <v>161202</v>
       </c>
       <c r="C73" t="s">
         <v>161</v>
@@ -3566,16 +3572,16 @@
         <v>13</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>33</v>
+        <v>158</v>
       </c>
       <c r="H73" s="3">
-        <v>200.0</v>
+        <v>250.0</v>
       </c>
       <c r="I73" s="3">
-        <v>5.1</v>
+        <v>8.3</v>
       </c>
       <c r="J73" s="3">
-        <v>194.9</v>
+        <v>241.7</v>
       </c>
       <c r="K73" t="s">
         <v>15</v>
@@ -3583,10 +3589,10 @@
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="1">
-        <v>92681</v>
+        <v>92754</v>
       </c>
       <c r="B74" s="1">
-        <v>161666</v>
+        <v>161225</v>
       </c>
       <c r="C74" t="s">
         <v>163</v>
@@ -3601,16 +3607,16 @@
         <v>13</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H74" s="3">
-        <v>140.0</v>
+        <v>200.0</v>
       </c>
       <c r="I74" s="3">
-        <v>2.69</v>
+        <v>5.1</v>
       </c>
       <c r="J74" s="3">
-        <v>137.31</v>
+        <v>194.9</v>
       </c>
       <c r="K74" t="s">
         <v>15</v>
@@ -3618,30 +3624,34 @@
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="1">
-        <v>92680</v>
+        <v>92778</v>
       </c>
       <c r="B75" s="1">
-        <v>161783</v>
+        <v>161666</v>
       </c>
       <c r="C75" t="s">
         <v>165</v>
       </c>
-      <c r="D75" s="2"/>
+      <c r="D75" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="E75" s="1">
         <v>30</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G75" s="1"/>
+      <c r="G75" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="H75" s="3">
-        <v>200.0</v>
+        <v>140.0</v>
       </c>
       <c r="I75" s="3">
-        <v>5.1</v>
+        <v>2.69</v>
       </c>
       <c r="J75" s="3">
-        <v>194.9</v>
+        <v>137.31</v>
       </c>
       <c r="K75" t="s">
         <v>15</v>
@@ -3649,34 +3659,30 @@
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="1">
-        <v>92679</v>
+        <v>92777</v>
       </c>
       <c r="B76" s="1">
-        <v>162042</v>
+        <v>161783</v>
       </c>
       <c r="C76" t="s">
-        <v>166</v>
-      </c>
-      <c r="D76" s="2" t="s">
         <v>167</v>
       </c>
+      <c r="D76" s="2"/>
       <c r="E76" s="1">
         <v>30</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G76" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="G76" s="1"/>
       <c r="H76" s="3">
-        <v>220.0</v>
+        <v>200.0</v>
       </c>
       <c r="I76" s="3">
-        <v>6.38</v>
+        <v>5.1</v>
       </c>
       <c r="J76" s="3">
-        <v>213.62</v>
+        <v>194.9</v>
       </c>
       <c r="K76" t="s">
         <v>15</v>
@@ -3684,16 +3690,16 @@
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="1">
-        <v>92678</v>
+        <v>92776</v>
       </c>
       <c r="B77" s="1">
-        <v>162077</v>
+        <v>162042</v>
       </c>
       <c r="C77" t="s">
         <v>168</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E77" s="1">
         <v>30</v>
@@ -3705,15 +3711,50 @@
         <v>14</v>
       </c>
       <c r="H77" s="3">
+        <v>220.0</v>
+      </c>
+      <c r="I77" s="3">
+        <v>6.38</v>
+      </c>
+      <c r="J77" s="3">
+        <v>213.62</v>
+      </c>
+      <c r="K77" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" s="1">
+        <v>92775</v>
+      </c>
+      <c r="B78" s="1">
+        <v>162077</v>
+      </c>
+      <c r="C78" t="s">
+        <v>170</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E78" s="1">
+        <v>30</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H78" s="3">
         <v>150.0</v>
       </c>
-      <c r="I77" s="3">
+      <c r="I78" s="3">
         <v>2.88</v>
       </c>
-      <c r="J77" s="3">
+      <c r="J78" s="3">
         <v>147.12</v>
       </c>
-      <c r="K77" t="s">
+      <c r="K78" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3755,7 +3796,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>3</v>
@@ -3770,13 +3811,13 @@
         <v>7</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K1" s="7" t="s">
         <v>9</v>
@@ -3785,21 +3826,21 @@
         <v>10</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="1">
-        <v>92634</v>
+        <v>92730</v>
       </c>
       <c r="B2" s="1">
         <v>15862</v>
       </c>
       <c r="C2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E2" s="1">
         <v>30</v>
@@ -3826,21 +3867,21 @@
         <v>15</v>
       </c>
       <c r="M2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1">
-        <v>92619</v>
+        <v>92715</v>
       </c>
       <c r="B3" s="1">
         <v>28826</v>
       </c>
       <c r="C3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E3" s="1">
         <v>30</v>
@@ -3867,21 +3908,21 @@
         <v>15</v>
       </c>
       <c r="M3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1">
-        <v>92617</v>
+        <v>92713</v>
       </c>
       <c r="B4" s="1">
         <v>32605</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E4" s="1">
         <v>30</v>
@@ -3908,21 +3949,21 @@
         <v>15</v>
       </c>
       <c r="M4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1">
-        <v>92660</v>
+        <v>92757</v>
       </c>
       <c r="B5" s="1">
         <v>32614</v>
       </c>
       <c r="C5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E5" s="1">
         <v>30</v>
@@ -3949,7 +3990,7 @@
         <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -3990,13 +4031,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>2</v>
@@ -4011,22 +4052,22 @@
         <v>5</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>7</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O1" s="7" t="s">
         <v>9</v>
@@ -4037,22 +4078,22 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1">
-        <v>92609</v>
+        <v>92705</v>
       </c>
       <c r="B2" s="1">
         <v>80161701</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D2" s="1">
         <v>10859</v>
       </c>
       <c r="E2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G2" s="1">
         <v>30</v>
@@ -4087,22 +4128,22 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1">
-        <v>92625</v>
+        <v>92721</v>
       </c>
       <c r="B3" s="1">
         <v>80161701</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D3" s="1">
         <v>17507</v>
       </c>
       <c r="E3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G3" s="1">
         <v>30</v>
@@ -4137,22 +4178,22 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1">
-        <v>92613</v>
+        <v>92709</v>
       </c>
       <c r="B4" s="1">
         <v>80161701</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D4" s="1">
         <v>25918</v>
       </c>
       <c r="E4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G4" s="1">
         <v>30</v>
@@ -4187,22 +4228,22 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1">
-        <v>92637</v>
+        <v>92733</v>
       </c>
       <c r="B5" s="1">
         <v>80161701</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D5" s="1">
         <v>31622</v>
       </c>
       <c r="E5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G5" s="1">
         <v>30</v>
@@ -4237,22 +4278,22 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1">
-        <v>92636</v>
+        <v>92732</v>
       </c>
       <c r="B6" s="1">
         <v>80161701</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D6" s="1">
         <v>31624</v>
       </c>
       <c r="E6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G6" s="1">
         <v>30</v>
@@ -4287,22 +4328,22 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1">
-        <v>92632</v>
+        <v>92728</v>
       </c>
       <c r="B7" s="1">
         <v>80161701</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D7" s="1">
         <v>31711</v>
       </c>
       <c r="E7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G7" s="1">
         <v>30</v>
